--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_geral.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_geral.xlsx
@@ -6306,7 +6306,9 @@
       <c r="AH18" s="14" t="n"/>
       <c r="AI18" s="14" t="n"/>
       <c r="AJ18" s="14" t="n"/>
-      <c r="AK18" s="7" t="n"/>
+      <c r="AK18" s="7" t="n">
+        <v>362</v>
+      </c>
       <c r="AL18" s="7" t="n">
         <v>10</v>
       </c>
@@ -8836,9 +8838,13 @@
       <c r="X36" s="12" t="n">
         <v>0.00233</v>
       </c>
-      <c r="Y36" s="7" t="n"/>
+      <c r="Y36" s="7" t="n">
+        <v>7</v>
+      </c>
       <c r="Z36" s="14" t="n"/>
-      <c r="AA36" s="14" t="n"/>
+      <c r="AA36" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="AB36" s="14" t="n"/>
       <c r="AC36" s="14" t="n"/>
       <c r="AD36" s="14" t="n"/>
@@ -8846,7 +8852,9 @@
       <c r="AF36" s="14" t="n"/>
       <c r="AG36" s="14" t="n"/>
       <c r="AH36" s="14" t="n"/>
-      <c r="AI36" s="14" t="n"/>
+      <c r="AI36" s="14" t="n">
+        <v>6</v>
+      </c>
       <c r="AJ36" s="14" t="n"/>
       <c r="AK36" s="7" t="n">
         <v>331</v>
@@ -8861,9 +8869,11 @@
         <v>1</v>
       </c>
       <c r="AO36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AP36" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ36" s="4" t="n">
         <v>0</v>
       </c>
@@ -9676,15 +9686,23 @@
         <v>41.6</v>
       </c>
       <c r="X42" s="12" t="n"/>
-      <c r="Y42" s="7" t="n"/>
+      <c r="Y42" s="7" t="n">
+        <v>29</v>
+      </c>
       <c r="Z42" s="14" t="n"/>
       <c r="AA42" s="14" t="n"/>
-      <c r="AB42" s="14" t="n"/>
+      <c r="AB42" s="14" t="n">
+        <v>38</v>
+      </c>
       <c r="AC42" s="14" t="n"/>
       <c r="AD42" s="14" t="n"/>
       <c r="AE42" s="14" t="n"/>
-      <c r="AF42" s="14" t="n"/>
-      <c r="AG42" s="14" t="n"/>
+      <c r="AF42" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG42" s="14" t="n">
+        <v>35</v>
+      </c>
       <c r="AH42" s="14" t="n"/>
       <c r="AI42" s="14" t="n"/>
       <c r="AJ42" s="14" t="n"/>
@@ -9697,9 +9715,11 @@
         <v>0</v>
       </c>
       <c r="AO42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AP42" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ42" s="4" t="n">
         <v>0</v>
       </c>
@@ -10871,15 +10891,23 @@
       <c r="X51" s="12" t="n">
         <v>0.03043</v>
       </c>
-      <c r="Y51" s="7" t="n"/>
+      <c r="Y51" s="7" t="n">
+        <v>9</v>
+      </c>
       <c r="Z51" s="14" t="n"/>
       <c r="AA51" s="14" t="n"/>
-      <c r="AB51" s="14" t="n"/>
+      <c r="AB51" s="14" t="n">
+        <v>36</v>
+      </c>
       <c r="AC51" s="14" t="n"/>
       <c r="AD51" s="14" t="n"/>
       <c r="AE51" s="14" t="n"/>
-      <c r="AF51" s="14" t="n"/>
-      <c r="AG51" s="14" t="n"/>
+      <c r="AF51" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG51" s="14" t="n">
+        <v>54</v>
+      </c>
       <c r="AH51" s="14" t="n"/>
       <c r="AI51" s="14" t="n"/>
       <c r="AJ51" s="14" t="n"/>
@@ -10894,9 +10922,11 @@
         <v>0</v>
       </c>
       <c r="AO51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AP51" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ51" s="4" t="n">
         <v>0</v>
       </c>

--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_geral.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_geral.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="geral" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="frequencias" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="dados" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="dicionario" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="geral" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="frequencias" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dados" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dicionario" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'geral'!$A$1:$O$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'geral'!$A$1:$O$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'frequencias'!$A$1:$D$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'dados'!$A$1:$AW$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'dicionario'!$A$1:$D$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'dados'!$A$1:$AZ$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'dicionario'!$A$1:$D$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>cesta_baixa</t>
+          <t>consumo_baixa</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível baixo (P25)</t>
+          <t>Consumo por pessoa (bebida + entrada ou prato), nível baixo (P25)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>cesta_mediana</t>
+          <t>consumo_mediana</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível mediano</t>
+          <t>Consumo por pessoa (bebida + entrada ou prato), nível mediano</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>cesta_alta</t>
+          <t>consumo_alta</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível alto (P75)</t>
+          <t>Consumo por pessoa (bebida + entrada ou prato), nível alto (P75)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>hamburguer_mediana</t>
+          <t>cesta_baixa</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Hambúrguer, mediana</t>
+          <t>Cesta completa (consumo + couvert encontrado), nível baixo (P25)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>batata_mediana</t>
+          <t>cesta_mediana</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Batata, mediana</t>
+          <t>Cesta completa (consumo + couvert encontrado), nível mediano</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>cerveja_mediana</t>
+          <t>cesta_alta</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Cerveja, mediana</t>
+          <t>Cesta completa (consumo + couvert encontrado), nível alto (P75)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>refrigerante_mediana</t>
+          <t>hamburguer_mediana</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Refrigerante, mediana</t>
+          <t>Hambúrguer, mediana</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>drinks_mediana</t>
+          <t>batata_mediana</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Drinks, mediana</t>
+          <t>Batata, mediana</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2714,24 +2714,24 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Acervo</t>
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Cardápio</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>titulos_acervo</t>
+          <t>cerveja_mediana</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Títulos no acervo publicado</t>
+          <t>Cerveja, mediana</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="E34" s="4">
@@ -2742,35 +2742,35 @@
         <f>ROWS(dados!$AK$2:$AK$55)-E34</f>
         <v/>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="14">
         <f>IFERROR(AVERAGE(dados!$AK$2:$AK$55),"")</f>
         <v/>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="14">
         <f>IFERROR(MEDIAN(dados!$AK$2:$AK$55),"")</f>
         <v/>
       </c>
-      <c r="I34" s="7">
+      <c r="I34" s="14">
         <f>IFERROR(STDEV(dados!$AK$2:$AK$55),"")</f>
         <v/>
       </c>
-      <c r="J34" s="7">
+      <c r="J34" s="14">
         <f>IFERROR(MIN(dados!$AK$2:$AK$55),"")</f>
         <v/>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="14">
         <f>IFERROR(PERCENTILE(dados!$AK$2:$AK$55,0.25),"")</f>
         <v/>
       </c>
-      <c r="L34" s="7">
+      <c r="L34" s="14">
         <f>IFERROR(PERCENTILE(dados!$AK$2:$AK$55,0.75),"")</f>
         <v/>
       </c>
-      <c r="M34" s="7">
+      <c r="M34" s="14">
         <f>IFERROR(MAX(dados!$AK$2:$AK$55),"")</f>
         <v/>
       </c>
-      <c r="N34" s="7">
+      <c r="N34" s="14">
         <f>IFERROR(M34-J34,"")</f>
         <v/>
       </c>
@@ -2780,24 +2780,24 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>B2</t>
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Cardápio</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>avaliacoes_b2</t>
+          <t>refrigerante_mediana</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Avaliações no recorte do B2 (até '3 meses atrás')</t>
+          <t>Refrigerante, mediana</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>avaliações</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="E35" s="4">
@@ -2808,35 +2808,35 @@
         <f>ROWS(dados!$AL$2:$AL$55)-E35</f>
         <v/>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="14">
         <f>IFERROR(AVERAGE(dados!$AL$2:$AL$55),"")</f>
         <v/>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="14">
         <f>IFERROR(MEDIAN(dados!$AL$2:$AL$55),"")</f>
         <v/>
       </c>
-      <c r="I35" s="7">
+      <c r="I35" s="14">
         <f>IFERROR(STDEV(dados!$AL$2:$AL$55),"")</f>
         <v/>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="14">
         <f>IFERROR(MIN(dados!$AL$2:$AL$55),"")</f>
         <v/>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="14">
         <f>IFERROR(PERCENTILE(dados!$AL$2:$AL$55,0.25),"")</f>
         <v/>
       </c>
-      <c r="L35" s="7">
+      <c r="L35" s="14">
         <f>IFERROR(PERCENTILE(dados!$AL$2:$AL$55,0.75),"")</f>
         <v/>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="14">
         <f>IFERROR(MAX(dados!$AL$2:$AL$55),"")</f>
         <v/>
       </c>
-      <c r="N35" s="7">
+      <c r="N35" s="14">
         <f>IFERROR(M35-J35,"")</f>
         <v/>
       </c>
@@ -2846,24 +2846,24 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>B2</t>
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Cardápio</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>avaliacoes_b2_com_texto</t>
+          <t>drinks_mediana</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Dessas, com texto</t>
+          <t>Drinks, mediana</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>avaliações</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="E36" s="4">
@@ -2874,35 +2874,35 @@
         <f>ROWS(dados!$AM$2:$AM$55)-E36</f>
         <v/>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="14">
         <f>IFERROR(AVERAGE(dados!$AM$2:$AM$55),"")</f>
         <v/>
       </c>
-      <c r="H36" s="7">
+      <c r="H36" s="14">
         <f>IFERROR(MEDIAN(dados!$AM$2:$AM$55),"")</f>
         <v/>
       </c>
-      <c r="I36" s="7">
+      <c r="I36" s="14">
         <f>IFERROR(STDEV(dados!$AM$2:$AM$55),"")</f>
         <v/>
       </c>
-      <c r="J36" s="7">
+      <c r="J36" s="14">
         <f>IFERROR(MIN(dados!$AM$2:$AM$55),"")</f>
         <v/>
       </c>
-      <c r="K36" s="7">
+      <c r="K36" s="14">
         <f>IFERROR(PERCENTILE(dados!$AM$2:$AM$55,0.25),"")</f>
         <v/>
       </c>
-      <c r="L36" s="7">
+      <c r="L36" s="14">
         <f>IFERROR(PERCENTILE(dados!$AM$2:$AM$55,0.75),"")</f>
         <v/>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="14">
         <f>IFERROR(MAX(dados!$AM$2:$AM$55),"")</f>
         <v/>
       </c>
-      <c r="N36" s="7">
+      <c r="N36" s="14">
         <f>IFERROR(M36-J36,"")</f>
         <v/>
       </c>
@@ -2911,8 +2911,206 @@
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>Acervo</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>titulos_acervo</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Títulos no acervo publicado</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>jogos</t>
+        </is>
+      </c>
+      <c r="E37" s="4">
+        <f>COUNT(dados!$AN$2:$AN$55)</f>
+        <v/>
+      </c>
+      <c r="F37" s="4">
+        <f>ROWS(dados!$AN$2:$AN$55)-E37</f>
+        <v/>
+      </c>
+      <c r="G37" s="7">
+        <f>IFERROR(AVERAGE(dados!$AN$2:$AN$55),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="7">
+        <f>IFERROR(MEDIAN(dados!$AN$2:$AN$55),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="7">
+        <f>IFERROR(STDEV(dados!$AN$2:$AN$55),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="7">
+        <f>IFERROR(MIN(dados!$AN$2:$AN$55),"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="7">
+        <f>IFERROR(PERCENTILE(dados!$AN$2:$AN$55,0.25),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="7">
+        <f>IFERROR(PERCENTILE(dados!$AN$2:$AN$55,0.75),"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="7">
+        <f>IFERROR(MAX(dados!$AN$2:$AN$55),"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="7">
+        <f>IFERROR(M37-J37,"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="6">
+        <f>IFERROR(I37/G37,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>avaliacoes_b2</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Avaliações no recorte do B2 (até '3 meses atrás')</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>avaliações</t>
+        </is>
+      </c>
+      <c r="E38" s="4">
+        <f>COUNT(dados!$AO$2:$AO$55)</f>
+        <v/>
+      </c>
+      <c r="F38" s="4">
+        <f>ROWS(dados!$AO$2:$AO$55)-E38</f>
+        <v/>
+      </c>
+      <c r="G38" s="7">
+        <f>IFERROR(AVERAGE(dados!$AO$2:$AO$55),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="7">
+        <f>IFERROR(MEDIAN(dados!$AO$2:$AO$55),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="7">
+        <f>IFERROR(STDEV(dados!$AO$2:$AO$55),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="7">
+        <f>IFERROR(MIN(dados!$AO$2:$AO$55),"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="7">
+        <f>IFERROR(PERCENTILE(dados!$AO$2:$AO$55,0.25),"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="7">
+        <f>IFERROR(PERCENTILE(dados!$AO$2:$AO$55,0.75),"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="7">
+        <f>IFERROR(MAX(dados!$AO$2:$AO$55),"")</f>
+        <v/>
+      </c>
+      <c r="N38" s="7">
+        <f>IFERROR(M38-J38,"")</f>
+        <v/>
+      </c>
+      <c r="O38" s="6">
+        <f>IFERROR(I38/G38,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>avaliacoes_b2_com_texto</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Dessas, com texto</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>avaliações</t>
+        </is>
+      </c>
+      <c r="E39" s="4">
+        <f>COUNT(dados!$AP$2:$AP$55)</f>
+        <v/>
+      </c>
+      <c r="F39" s="4">
+        <f>ROWS(dados!$AP$2:$AP$55)-E39</f>
+        <v/>
+      </c>
+      <c r="G39" s="7">
+        <f>IFERROR(AVERAGE(dados!$AP$2:$AP$55),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="7">
+        <f>IFERROR(MEDIAN(dados!$AP$2:$AP$55),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="7">
+        <f>IFERROR(STDEV(dados!$AP$2:$AP$55),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="7">
+        <f>IFERROR(MIN(dados!$AP$2:$AP$55),"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="7">
+        <f>IFERROR(PERCENTILE(dados!$AP$2:$AP$55,0.25),"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="7">
+        <f>IFERROR(PERCENTILE(dados!$AP$2:$AP$55,0.75),"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="7">
+        <f>IFERROR(MAX(dados!$AP$2:$AP$55),"")</f>
+        <v/>
+      </c>
+      <c r="N39" s="7">
+        <f>IFERROR(M39-J39,"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="6">
+        <f>IFERROR(I39/G39,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O36"/>
+  <autoFilter ref="A1:O39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3428,11 +3626,11 @@
         </is>
       </c>
       <c r="C26" s="4">
-        <f>SUM(dados!$AN$2:$AN$55)</f>
+        <f>SUM(dados!$AQ$2:$AQ$55)</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IFERROR(SUM(dados!$AN$2:$AN$55)/COUNT(dados!$AN$2:$AN$55),"")</f>
+        <f>IFERROR(SUM(dados!$AQ$2:$AQ$55)/COUNT(dados!$AQ$2:$AQ$55),"")</f>
         <v/>
       </c>
     </row>
@@ -3448,11 +3646,11 @@
         </is>
       </c>
       <c r="C27" s="4">
-        <f>SUM(dados!$AO$2:$AO$55)</f>
+        <f>SUM(dados!$AR$2:$AR$55)</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IFERROR(SUM(dados!$AO$2:$AO$55)/COUNT(dados!$AO$2:$AO$55),"")</f>
+        <f>IFERROR(SUM(dados!$AR$2:$AR$55)/COUNT(dados!$AR$2:$AR$55),"")</f>
         <v/>
       </c>
     </row>
@@ -3468,11 +3666,11 @@
         </is>
       </c>
       <c r="C28" s="4">
-        <f>SUM(dados!$AP$2:$AP$55)</f>
+        <f>SUM(dados!$AS$2:$AS$55)</f>
         <v/>
       </c>
       <c r="D28" s="17">
-        <f>IFERROR(SUM(dados!$AP$2:$AP$55)/COUNT(dados!$AP$2:$AP$55),"")</f>
+        <f>IFERROR(SUM(dados!$AS$2:$AS$55)/COUNT(dados!$AS$2:$AS$55),"")</f>
         <v/>
       </c>
     </row>
@@ -3488,11 +3686,11 @@
         </is>
       </c>
       <c r="C29" s="4">
-        <f>SUM(dados!$AQ$2:$AQ$55)</f>
+        <f>SUM(dados!$AT$2:$AT$55)</f>
         <v/>
       </c>
       <c r="D29" s="17">
-        <f>IFERROR(SUM(dados!$AQ$2:$AQ$55)/COUNT(dados!$AQ$2:$AQ$55),"")</f>
+        <f>IFERROR(SUM(dados!$AT$2:$AT$55)/COUNT(dados!$AT$2:$AT$55),"")</f>
         <v/>
       </c>
     </row>
@@ -3508,11 +3706,11 @@
         </is>
       </c>
       <c r="C30" s="4">
-        <f>SUM(dados!$AR$2:$AR$55)</f>
+        <f>SUM(dados!$AU$2:$AU$55)</f>
         <v/>
       </c>
       <c r="D30" s="17">
-        <f>IFERROR(SUM(dados!$AR$2:$AR$55)/COUNT(dados!$AR$2:$AR$55),"")</f>
+        <f>IFERROR(SUM(dados!$AU$2:$AU$55)/COUNT(dados!$AU$2:$AU$55),"")</f>
         <v/>
       </c>
     </row>
@@ -3528,11 +3726,11 @@
         </is>
       </c>
       <c r="C31" s="4">
-        <f>SUM(dados!$AS$2:$AS$55)</f>
+        <f>SUM(dados!$AV$2:$AV$55)</f>
         <v/>
       </c>
       <c r="D31" s="17">
-        <f>IFERROR(SUM(dados!$AS$2:$AS$55)/COUNT(dados!$AS$2:$AS$55),"")</f>
+        <f>IFERROR(SUM(dados!$AV$2:$AV$55)/COUNT(dados!$AV$2:$AV$55),"")</f>
         <v/>
       </c>
     </row>
@@ -3548,11 +3746,11 @@
         </is>
       </c>
       <c r="C32" s="4">
-        <f>SUM(dados!$AT$2:$AT$55)</f>
+        <f>SUM(dados!$AW$2:$AW$55)</f>
         <v/>
       </c>
       <c r="D32" s="17">
-        <f>IFERROR(SUM(dados!$AT$2:$AT$55)/COUNT(dados!$AT$2:$AT$55),"")</f>
+        <f>IFERROR(SUM(dados!$AW$2:$AW$55)/COUNT(dados!$AW$2:$AW$55),"")</f>
         <v/>
       </c>
     </row>
@@ -3568,11 +3766,11 @@
         </is>
       </c>
       <c r="C33" s="4">
-        <f>SUM(dados!$AU$2:$AU$55)</f>
+        <f>SUM(dados!$AX$2:$AX$55)</f>
         <v/>
       </c>
       <c r="D33" s="17">
-        <f>IFERROR(SUM(dados!$AU$2:$AU$55)/COUNT(dados!$AU$2:$AU$55),"")</f>
+        <f>IFERROR(SUM(dados!$AX$2:$AX$55)/COUNT(dados!$AX$2:$AX$55),"")</f>
         <v/>
       </c>
     </row>
@@ -3588,11 +3786,11 @@
         </is>
       </c>
       <c r="C34" s="4">
-        <f>SUM(dados!$AV$2:$AV$55)</f>
+        <f>SUM(dados!$AY$2:$AY$55)</f>
         <v/>
       </c>
       <c r="D34" s="17">
-        <f>IFERROR(SUM(dados!$AV$2:$AV$55)/COUNT(dados!$AV$2:$AV$55),"")</f>
+        <f>IFERROR(SUM(dados!$AY$2:$AY$55)/COUNT(dados!$AY$2:$AY$55),"")</f>
         <v/>
       </c>
     </row>
@@ -3608,11 +3806,11 @@
         </is>
       </c>
       <c r="C35" s="4">
-        <f>SUM(dados!$AW$2:$AW$55)</f>
+        <f>SUM(dados!$AZ$2:$AZ$55)</f>
         <v/>
       </c>
       <c r="D35" s="17">
-        <f>IFERROR(SUM(dados!$AW$2:$AW$55)/COUNT(dados!$AW$2:$AW$55),"")</f>
+        <f>IFERROR(SUM(dados!$AZ$2:$AZ$55)/COUNT(dados!$AZ$2:$AZ$55),"")</f>
         <v/>
       </c>
     </row>
@@ -3628,7 +3826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3680,6 +3878,9 @@
     <col width="12" customWidth="1" min="47" max="47"/>
     <col width="12" customWidth="1" min="48" max="48"/>
     <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3825,105 +4026,120 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>consumo_baixa</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>consumo_mediana</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>consumo_alta</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>cesta_baixa</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>cesta_mediana</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>cesta_alta</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>hamburguer_mediana</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>batata_mediana</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>cerveja_mediana</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>refrigerante_mediana</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>drinks_mediana</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>titulos_acervo</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>avaliacoes_b2</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>avaliacoes_b2_com_texto</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>tem_metro_1000m</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>tem_cardapio</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>cobra_couvert</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>abre_segunda</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>abre_terca</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>abre_quarta</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>abre_quinta</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>abre_sexta</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>abre_sabado</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>abre_domingo</t>
         </is>
@@ -4029,35 +4245,29 @@
       <c r="AE2" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="AF2" s="14" t="n">
+      <c r="AF2" s="14" t="n"/>
+      <c r="AG2" s="14" t="n"/>
+      <c r="AH2" s="14" t="n"/>
+      <c r="AI2" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="AG2" s="14" t="n">
+      <c r="AJ2" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="AH2" s="14" t="n">
+      <c r="AK2" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AI2" s="14" t="n">
+      <c r="AL2" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="AJ2" s="14" t="n"/>
-      <c r="AK2" s="7" t="n"/>
-      <c r="AL2" s="7" t="n">
+      <c r="AM2" s="14" t="n"/>
+      <c r="AN2" s="7" t="n"/>
+      <c r="AO2" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="AM2" s="7" t="n">
+      <c r="AP2" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP2" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ2" s="4" t="n">
         <v>1</v>
       </c>
@@ -4065,7 +4275,7 @@
         <v>1</v>
       </c>
       <c r="AS2" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT2" s="4" t="n">
         <v>1</v>
@@ -4077,6 +4287,15 @@
         <v>1</v>
       </c>
       <c r="AW2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4169,31 +4388,25 @@
       <c r="AH3" s="14" t="n"/>
       <c r="AI3" s="14" t="n"/>
       <c r="AJ3" s="14" t="n"/>
-      <c r="AK3" s="7" t="n"/>
-      <c r="AL3" s="7" t="n">
+      <c r="AK3" s="14" t="n"/>
+      <c r="AL3" s="14" t="n"/>
+      <c r="AM3" s="14" t="n"/>
+      <c r="AN3" s="7" t="n"/>
+      <c r="AO3" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="AM3" s="7" t="n">
+      <c r="AP3" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AN3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="4" t="n"/>
       <c r="AQ3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS3" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4" t="n"/>
       <c r="AT3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU3" s="4" t="n">
         <v>1</v>
@@ -4202,6 +4415,15 @@
         <v>1</v>
       </c>
       <c r="AW3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4307,40 +4529,34 @@
       </c>
       <c r="AF4" s="14" t="n"/>
       <c r="AG4" s="14" t="n"/>
-      <c r="AH4" s="14" t="n">
+      <c r="AH4" s="14" t="n"/>
+      <c r="AI4" s="14" t="n"/>
+      <c r="AJ4" s="14" t="n"/>
+      <c r="AK4" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AI4" s="14" t="n">
+      <c r="AL4" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="AJ4" s="14" t="n"/>
-      <c r="AK4" s="7" t="n"/>
-      <c r="AL4" s="7" t="n">
+      <c r="AM4" s="14" t="n"/>
+      <c r="AN4" s="7" t="n"/>
+      <c r="AO4" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="AM4" s="7" t="n">
+      <c r="AP4" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AN4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP4" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AS4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" s="4" t="n">
         <v>1</v>
@@ -4349,6 +4565,15 @@
         <v>1</v>
       </c>
       <c r="AW4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ4" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4442,47 +4667,47 @@
         <v>33</v>
       </c>
       <c r="AC5" s="14" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="AD5" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE5" s="14" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="AF5" s="14" t="n">
         <v>54.5</v>
       </c>
-      <c r="AD5" s="14" t="n">
+      <c r="AG5" s="14" t="n">
         <v>67.5</v>
       </c>
-      <c r="AE5" s="14" t="n">
+      <c r="AH5" s="14" t="n">
         <v>81.5</v>
       </c>
-      <c r="AF5" s="14" t="n">
+      <c r="AI5" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="AG5" s="14" t="n">
+      <c r="AJ5" s="14" t="n">
         <v>30.5</v>
       </c>
-      <c r="AH5" s="14" t="n">
+      <c r="AK5" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AI5" s="14" t="n">
+      <c r="AL5" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AJ5" s="14" t="n">
+      <c r="AM5" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="AK5" s="7" t="n">
+      <c r="AN5" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="AL5" s="7" t="n">
+      <c r="AO5" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="AM5" s="7" t="n">
+      <c r="AP5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="AN5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ5" s="4" t="n">
         <v>1</v>
       </c>
@@ -4502,6 +4727,15 @@
         <v>1</v>
       </c>
       <c r="AW5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4599,45 +4833,45 @@
         <v>31</v>
       </c>
       <c r="AC6" s="14" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="AD6" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE6" s="14" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="AF6" s="14" t="n">
         <v>64.5</v>
       </c>
-      <c r="AD6" s="14" t="n">
+      <c r="AG6" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="AE6" s="14" t="n">
+      <c r="AH6" s="14" t="n">
         <v>76.75</v>
       </c>
-      <c r="AF6" s="14" t="n"/>
-      <c r="AG6" s="14" t="n"/>
-      <c r="AH6" s="14" t="n">
+      <c r="AI6" s="14" t="n"/>
+      <c r="AJ6" s="14" t="n"/>
+      <c r="AK6" s="14" t="n">
         <v>8.5</v>
       </c>
-      <c r="AI6" s="14" t="n">
+      <c r="AL6" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AJ6" s="14" t="n">
+      <c r="AM6" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="AK6" s="7" t="n">
+      <c r="AN6" s="7" t="n">
         <v>952</v>
       </c>
-      <c r="AL6" s="7" t="n">
+      <c r="AO6" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="AM6" s="7" t="n">
+      <c r="AP6" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="AN6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP6" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR6" s="4" t="n">
         <v>1</v>
@@ -4646,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="AT6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU6" s="4" t="n">
         <v>1</v>
@@ -4655,6 +4889,15 @@
         <v>1</v>
       </c>
       <c r="AW6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4759,32 +5002,26 @@
         <v>84.5</v>
       </c>
       <c r="AF7" s="14" t="n"/>
-      <c r="AG7" s="14" t="n">
+      <c r="AG7" s="14" t="n"/>
+      <c r="AH7" s="14" t="n"/>
+      <c r="AI7" s="14" t="n"/>
+      <c r="AJ7" s="14" t="n">
         <v>25.5</v>
       </c>
-      <c r="AH7" s="14" t="n">
+      <c r="AK7" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="AI7" s="14" t="n">
+      <c r="AL7" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AJ7" s="14" t="n"/>
-      <c r="AK7" s="7" t="n"/>
-      <c r="AL7" s="7" t="n">
+      <c r="AM7" s="14" t="n"/>
+      <c r="AN7" s="7" t="n"/>
+      <c r="AO7" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="AM7" s="7" t="n">
+      <c r="AP7" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="AN7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP7" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ7" s="4" t="n">
         <v>0</v>
       </c>
@@ -4792,10 +5029,10 @@
         <v>1</v>
       </c>
       <c r="AS7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU7" s="4" t="n">
         <v>1</v>
@@ -4804,6 +5041,15 @@
         <v>1</v>
       </c>
       <c r="AW7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4898,31 +5144,25 @@
       <c r="AH8" s="14" t="n"/>
       <c r="AI8" s="14" t="n"/>
       <c r="AJ8" s="14" t="n"/>
-      <c r="AK8" s="7" t="n">
+      <c r="AK8" s="14" t="n"/>
+      <c r="AL8" s="14" t="n"/>
+      <c r="AM8" s="14" t="n"/>
+      <c r="AN8" s="7" t="n">
         <v>214</v>
       </c>
-      <c r="AL8" s="7" t="n">
+      <c r="AO8" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="AM8" s="7" t="n">
+      <c r="AP8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AN8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="4" t="n"/>
       <c r="AQ8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS8" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4" t="n"/>
       <c r="AT8" s="4" t="n">
         <v>1</v>
       </c>
@@ -4933,6 +5173,15 @@
         <v>1</v>
       </c>
       <c r="AW8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5032,58 +5281,61 @@
       <c r="AE9" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="AF9" s="14" t="n">
+      <c r="AF9" s="14" t="n"/>
+      <c r="AG9" s="14" t="n"/>
+      <c r="AH9" s="14" t="n"/>
+      <c r="AI9" s="14" t="n">
         <v>29.5</v>
       </c>
-      <c r="AG9" s="14" t="n">
+      <c r="AJ9" s="14" t="n">
         <v>26.5</v>
       </c>
-      <c r="AH9" s="14" t="n">
+      <c r="AK9" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="AI9" s="14" t="n">
+      <c r="AL9" s="14" t="n">
         <v>7.5</v>
       </c>
-      <c r="AJ9" s="14" t="n">
+      <c r="AM9" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="AK9" s="7" t="n">
+      <c r="AN9" s="7" t="n">
         <v>1833</v>
       </c>
-      <c r="AL9" s="7" t="n">
+      <c r="AO9" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AM9" s="7" t="n">
+      <c r="AP9" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AN9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5160,29 +5412,23 @@
       <c r="AH10" s="14" t="n"/>
       <c r="AI10" s="14" t="n"/>
       <c r="AJ10" s="14" t="n"/>
-      <c r="AK10" s="7" t="n"/>
-      <c r="AL10" s="7" t="n">
+      <c r="AK10" s="14" t="n"/>
+      <c r="AL10" s="14" t="n"/>
+      <c r="AM10" s="14" t="n"/>
+      <c r="AN10" s="7" t="n"/>
+      <c r="AO10" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="AM10" s="7" t="n">
+      <c r="AP10" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="AN10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AR10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS10" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS10" s="4" t="n"/>
       <c r="AT10" s="4" t="n">
         <v>1</v>
       </c>
@@ -5193,6 +5439,15 @@
         <v>1</v>
       </c>
       <c r="AW10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5296,54 +5551,57 @@
       <c r="AE11" s="14" t="n">
         <v>37.5</v>
       </c>
-      <c r="AF11" s="14" t="n">
+      <c r="AF11" s="14" t="n"/>
+      <c r="AG11" s="14" t="n"/>
+      <c r="AH11" s="14" t="n"/>
+      <c r="AI11" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="AG11" s="14" t="n">
+      <c r="AJ11" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="AH11" s="14" t="n">
+      <c r="AK11" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AI11" s="14" t="n"/>
-      <c r="AJ11" s="14" t="n"/>
-      <c r="AK11" s="7" t="n">
+      <c r="AL11" s="14" t="n"/>
+      <c r="AM11" s="14" t="n"/>
+      <c r="AN11" s="7" t="n">
         <v>312</v>
       </c>
-      <c r="AL11" s="7" t="n">
+      <c r="AO11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="AM11" s="7" t="n">
+      <c r="AP11" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AN11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP11" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AT11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ11" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5447,39 +5705,33 @@
       <c r="AE12" s="14" t="n">
         <v>60.5</v>
       </c>
-      <c r="AF12" s="14" t="n">
+      <c r="AF12" s="14" t="n"/>
+      <c r="AG12" s="14" t="n"/>
+      <c r="AH12" s="14" t="n"/>
+      <c r="AI12" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="AG12" s="14" t="n">
+      <c r="AJ12" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="AH12" s="14" t="n">
+      <c r="AK12" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AI12" s="14" t="n">
+      <c r="AL12" s="14" t="n">
         <v>8.9</v>
       </c>
-      <c r="AJ12" s="14" t="n">
+      <c r="AM12" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AK12" s="7" t="n">
+      <c r="AN12" s="7" t="n">
         <v>370</v>
       </c>
-      <c r="AL12" s="7" t="n">
+      <c r="AO12" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AM12" s="7" t="n">
+      <c r="AP12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="AN12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP12" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ12" s="4" t="n">
         <v>1</v>
       </c>
@@ -5487,7 +5739,7 @@
         <v>1</v>
       </c>
       <c r="AS12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT12" s="4" t="n">
         <v>1</v>
@@ -5499,6 +5751,15 @@
         <v>1</v>
       </c>
       <c r="AW12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5594,66 +5855,75 @@
         <v>35</v>
       </c>
       <c r="AC13" s="14" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AD13" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE13" s="14" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AF13" s="14" t="n">
         <v>56.75</v>
       </c>
-      <c r="AD13" s="14" t="n">
+      <c r="AG13" s="14" t="n">
         <v>73.5</v>
       </c>
-      <c r="AE13" s="14" t="n">
+      <c r="AH13" s="14" t="n">
         <v>81.25</v>
       </c>
-      <c r="AF13" s="14" t="n">
+      <c r="AI13" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="AG13" s="14" t="n">
+      <c r="AJ13" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="AH13" s="14" t="n">
+      <c r="AK13" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="AI13" s="14" t="n">
+      <c r="AL13" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="AJ13" s="14" t="n">
+      <c r="AM13" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="AK13" s="7" t="n">
+      <c r="AN13" s="7" t="n">
         <v>468</v>
       </c>
-      <c r="AL13" s="7" t="n">
+      <c r="AO13" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="AM13" s="7" t="n">
+      <c r="AP13" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="AN13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP13" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AT13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ13" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5753,52 +6023,55 @@
       <c r="AE14" s="14" t="n">
         <v>71.5</v>
       </c>
-      <c r="AF14" s="14" t="n">
+      <c r="AF14" s="14" t="n"/>
+      <c r="AG14" s="14" t="n"/>
+      <c r="AH14" s="14" t="n"/>
+      <c r="AI14" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="AG14" s="14" t="n"/>
-      <c r="AH14" s="14" t="n">
+      <c r="AJ14" s="14" t="n"/>
+      <c r="AK14" s="14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AI14" s="14" t="n">
+      <c r="AL14" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AJ14" s="14" t="n">
+      <c r="AM14" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="AK14" s="7" t="n">
+      <c r="AN14" s="7" t="n">
         <v>588</v>
       </c>
-      <c r="AL14" s="7" t="n"/>
-      <c r="AM14" s="7" t="n"/>
-      <c r="AN14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP14" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO14" s="7" t="n"/>
+      <c r="AP14" s="7" t="n"/>
       <c r="AQ14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5896,62 +6169,71 @@
         <v>50</v>
       </c>
       <c r="AC15" s="14" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="AD15" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="AE15" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF15" s="14" t="n">
         <v>71</v>
       </c>
-      <c r="AD15" s="14" t="n">
+      <c r="AG15" s="14" t="n">
         <v>85.5</v>
       </c>
-      <c r="AE15" s="14" t="n">
+      <c r="AH15" s="14" t="n">
         <v>98.75</v>
       </c>
-      <c r="AF15" s="14" t="n">
+      <c r="AI15" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="AG15" s="14" t="n"/>
-      <c r="AH15" s="14" t="n">
+      <c r="AJ15" s="14" t="n"/>
+      <c r="AK15" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AI15" s="14" t="n"/>
-      <c r="AJ15" s="14" t="n">
+      <c r="AL15" s="14" t="n"/>
+      <c r="AM15" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="AK15" s="7" t="n">
+      <c r="AN15" s="7" t="n">
         <v>190</v>
       </c>
-      <c r="AL15" s="7" t="n">
+      <c r="AO15" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="AM15" s="7" t="n">
+      <c r="AP15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AN15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP15" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AT15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ15" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6046,31 +6328,25 @@
       <c r="AH16" s="14" t="n"/>
       <c r="AI16" s="14" t="n"/>
       <c r="AJ16" s="14" t="n"/>
-      <c r="AK16" s="7" t="n"/>
-      <c r="AL16" s="7" t="n">
+      <c r="AK16" s="14" t="n"/>
+      <c r="AL16" s="14" t="n"/>
+      <c r="AM16" s="14" t="n"/>
+      <c r="AN16" s="7" t="n"/>
+      <c r="AO16" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="AM16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" s="4" t="n"/>
+      <c r="AP16" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="AQ16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS16" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS16" s="4" t="n"/>
       <c r="AT16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU16" s="4" t="n">
         <v>1</v>
@@ -6079,6 +6355,15 @@
         <v>1</v>
       </c>
       <c r="AW16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ16" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6170,62 +6455,71 @@
         <v>35</v>
       </c>
       <c r="AC17" s="14" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AD17" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE17" s="14" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AF17" s="14" t="n">
         <v>58.5</v>
       </c>
-      <c r="AD17" s="14" t="n">
+      <c r="AG17" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AE17" s="14" t="n">
+      <c r="AH17" s="14" t="n">
         <v>87.5</v>
       </c>
-      <c r="AF17" s="14" t="n">
+      <c r="AI17" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="AG17" s="14" t="n">
+      <c r="AJ17" s="14" t="n">
         <v>37.5</v>
       </c>
-      <c r="AH17" s="14" t="n">
+      <c r="AK17" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AI17" s="14" t="n">
+      <c r="AL17" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AJ17" s="14" t="n">
+      <c r="AM17" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="AK17" s="7" t="n">
+      <c r="AN17" s="7" t="n">
         <v>192</v>
       </c>
-      <c r="AL17" s="7" t="n"/>
-      <c r="AM17" s="7" t="n"/>
-      <c r="AN17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP17" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AO17" s="7" t="n"/>
+      <c r="AP17" s="7" t="n"/>
       <c r="AQ17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AT17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ17" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6306,33 +6600,27 @@
       <c r="AH18" s="14" t="n"/>
       <c r="AI18" s="14" t="n"/>
       <c r="AJ18" s="14" t="n"/>
-      <c r="AK18" s="7" t="n">
+      <c r="AK18" s="14" t="n"/>
+      <c r="AL18" s="14" t="n"/>
+      <c r="AM18" s="14" t="n"/>
+      <c r="AN18" s="7" t="n">
         <v>362</v>
       </c>
-      <c r="AL18" s="7" t="n">
+      <c r="AO18" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="AM18" s="7" t="n">
+      <c r="AP18" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AN18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS18" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS18" s="4" t="n"/>
       <c r="AT18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU18" s="4" t="n">
         <v>1</v>
@@ -6341,6 +6629,15 @@
         <v>1</v>
       </c>
       <c r="AW18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ18" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6434,47 +6731,47 @@
         <v>52</v>
       </c>
       <c r="AC19" s="14" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AD19" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="AE19" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="AF19" s="14" t="n">
         <v>74</v>
       </c>
-      <c r="AD19" s="14" t="n">
+      <c r="AG19" s="14" t="n">
         <v>97</v>
       </c>
-      <c r="AE19" s="14" t="n">
+      <c r="AH19" s="14" t="n">
         <v>121</v>
       </c>
-      <c r="AF19" s="14" t="n">
+      <c r="AI19" s="14" t="n">
         <v>54</v>
       </c>
-      <c r="AG19" s="14" t="n">
+      <c r="AJ19" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="AH19" s="14" t="n">
+      <c r="AK19" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="AI19" s="14" t="n">
+      <c r="AL19" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AJ19" s="14" t="n">
+      <c r="AM19" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AK19" s="7" t="n">
+      <c r="AN19" s="7" t="n">
         <v>836</v>
       </c>
-      <c r="AL19" s="7" t="n">
+      <c r="AO19" s="7" t="n">
         <v>272</v>
       </c>
-      <c r="AM19" s="7" t="n">
+      <c r="AP19" s="7" t="n">
         <v>243</v>
       </c>
-      <c r="AN19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP19" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ19" s="4" t="n">
         <v>0</v>
       </c>
@@ -6485,7 +6782,7 @@
         <v>1</v>
       </c>
       <c r="AT19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU19" s="4" t="n">
         <v>1</v>
@@ -6494,6 +6791,15 @@
         <v>1</v>
       </c>
       <c r="AW19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6586,39 +6892,42 @@
       <c r="AH20" s="14" t="n"/>
       <c r="AI20" s="14" t="n"/>
       <c r="AJ20" s="14" t="n"/>
-      <c r="AK20" s="7" t="n"/>
-      <c r="AL20" s="7" t="n">
+      <c r="AK20" s="14" t="n"/>
+      <c r="AL20" s="14" t="n"/>
+      <c r="AM20" s="14" t="n"/>
+      <c r="AN20" s="7" t="n"/>
+      <c r="AO20" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AM20" s="7" t="n">
+      <c r="AP20" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AN20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AS20" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS20" s="4" t="n"/>
       <c r="AT20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ20" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6722,56 +7031,59 @@
       <c r="AE21" s="14" t="n">
         <v>54.5</v>
       </c>
-      <c r="AF21" s="14" t="n">
+      <c r="AF21" s="14" t="n"/>
+      <c r="AG21" s="14" t="n"/>
+      <c r="AH21" s="14" t="n"/>
+      <c r="AI21" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="AG21" s="14" t="n">
+      <c r="AJ21" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="AH21" s="14" t="n">
+      <c r="AK21" s="14" t="n">
         <v>16.5</v>
       </c>
-      <c r="AI21" s="14" t="n">
+      <c r="AL21" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="AJ21" s="14" t="n"/>
-      <c r="AK21" s="7" t="n">
+      <c r="AM21" s="14" t="n"/>
+      <c r="AN21" s="7" t="n">
         <v>780</v>
       </c>
-      <c r="AL21" s="7" t="n">
+      <c r="AO21" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="AM21" s="7" t="n">
+      <c r="AP21" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="AN21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP21" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ21" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6868,31 +7180,25 @@
       <c r="AH22" s="14" t="n"/>
       <c r="AI22" s="14" t="n"/>
       <c r="AJ22" s="14" t="n"/>
-      <c r="AK22" s="7" t="n"/>
-      <c r="AL22" s="7" t="n">
+      <c r="AK22" s="14" t="n"/>
+      <c r="AL22" s="14" t="n"/>
+      <c r="AM22" s="14" t="n"/>
+      <c r="AN22" s="7" t="n"/>
+      <c r="AO22" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AM22" s="7" t="n">
+      <c r="AP22" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AN22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="4" t="n"/>
       <c r="AQ22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS22" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS22" s="4" t="n"/>
       <c r="AT22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU22" s="4" t="n">
         <v>1</v>
@@ -6901,6 +7207,15 @@
         <v>1</v>
       </c>
       <c r="AW22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ22" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6993,29 +7308,23 @@
       <c r="AH23" s="14" t="n"/>
       <c r="AI23" s="14" t="n"/>
       <c r="AJ23" s="14" t="n"/>
-      <c r="AK23" s="7" t="n"/>
-      <c r="AL23" s="7" t="n">
+      <c r="AK23" s="14" t="n"/>
+      <c r="AL23" s="14" t="n"/>
+      <c r="AM23" s="14" t="n"/>
+      <c r="AN23" s="7" t="n"/>
+      <c r="AO23" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="AM23" s="7" t="n">
+      <c r="AP23" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AN23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="4" t="n"/>
       <c r="AQ23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AR23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS23" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS23" s="4" t="n"/>
       <c r="AT23" s="4" t="n">
         <v>1</v>
       </c>
@@ -7026,6 +7335,15 @@
         <v>1</v>
       </c>
       <c r="AW23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ23" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7112,29 +7430,23 @@
       <c r="AH24" s="14" t="n"/>
       <c r="AI24" s="14" t="n"/>
       <c r="AJ24" s="14" t="n"/>
-      <c r="AK24" s="7" t="n">
+      <c r="AK24" s="14" t="n"/>
+      <c r="AL24" s="14" t="n"/>
+      <c r="AM24" s="14" t="n"/>
+      <c r="AN24" s="7" t="n">
         <v>1357</v>
       </c>
-      <c r="AL24" s="7" t="n"/>
-      <c r="AM24" s="7" t="n"/>
-      <c r="AN24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" s="4" t="n"/>
+      <c r="AO24" s="7" t="n"/>
+      <c r="AP24" s="7" t="n"/>
       <c r="AQ24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS24" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS24" s="4" t="n"/>
       <c r="AT24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU24" s="4" t="n">
         <v>1</v>
@@ -7143,6 +7455,15 @@
         <v>1</v>
       </c>
       <c r="AW24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ24" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7240,66 +7561,75 @@
         <v>45</v>
       </c>
       <c r="AC25" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AD25" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="AE25" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="AF25" s="14" t="n">
         <v>52.25</v>
       </c>
-      <c r="AD25" s="14" t="n">
+      <c r="AG25" s="14" t="n">
         <v>68.5</v>
       </c>
-      <c r="AE25" s="14" t="n">
+      <c r="AH25" s="14" t="n">
         <v>96.75</v>
       </c>
-      <c r="AF25" s="14" t="n">
+      <c r="AI25" s="14" t="n">
         <v>52.5</v>
       </c>
-      <c r="AG25" s="14" t="n">
+      <c r="AJ25" s="14" t="n">
         <v>28.5</v>
       </c>
-      <c r="AH25" s="14" t="n">
+      <c r="AK25" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="AI25" s="14" t="n">
+      <c r="AL25" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AJ25" s="14" t="n">
+      <c r="AM25" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="AK25" s="7" t="n">
+      <c r="AN25" s="7" t="n">
         <v>540</v>
       </c>
-      <c r="AL25" s="7" t="n">
+      <c r="AO25" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="AM25" s="7" t="n">
+      <c r="AP25" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="AN25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP25" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AT25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ25" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7399,39 +7729,33 @@
       <c r="AE26" s="14" t="n">
         <v>76</v>
       </c>
-      <c r="AF26" s="14" t="n">
+      <c r="AF26" s="14" t="n"/>
+      <c r="AG26" s="14" t="n"/>
+      <c r="AH26" s="14" t="n"/>
+      <c r="AI26" s="14" t="n">
         <v>49.5</v>
       </c>
-      <c r="AG26" s="14" t="n">
+      <c r="AJ26" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="AH26" s="14" t="n">
+      <c r="AK26" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="AI26" s="14" t="n">
+      <c r="AL26" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AJ26" s="14" t="n">
+      <c r="AM26" s="14" t="n">
         <v>36.5</v>
       </c>
-      <c r="AK26" s="7" t="n">
+      <c r="AN26" s="7" t="n">
         <v>934</v>
       </c>
-      <c r="AL26" s="7" t="n">
+      <c r="AO26" s="7" t="n">
         <v>712</v>
       </c>
-      <c r="AM26" s="7" t="n">
+      <c r="AP26" s="7" t="n">
         <v>453</v>
       </c>
-      <c r="AN26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ26" s="4" t="n">
         <v>1</v>
       </c>
@@ -7439,7 +7763,7 @@
         <v>1</v>
       </c>
       <c r="AS26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT26" s="4" t="n">
         <v>1</v>
@@ -7451,6 +7775,15 @@
         <v>1</v>
       </c>
       <c r="AW26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ26" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7543,31 +7876,25 @@
       <c r="AH27" s="14" t="n"/>
       <c r="AI27" s="14" t="n"/>
       <c r="AJ27" s="14" t="n"/>
-      <c r="AK27" s="7" t="n"/>
-      <c r="AL27" s="7" t="n">
+      <c r="AK27" s="14" t="n"/>
+      <c r="AL27" s="14" t="n"/>
+      <c r="AM27" s="14" t="n"/>
+      <c r="AN27" s="7" t="n"/>
+      <c r="AO27" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="AM27" s="7" t="n">
+      <c r="AP27" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="AN27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="4" t="n"/>
       <c r="AQ27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS27" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS27" s="4" t="n"/>
       <c r="AT27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU27" s="4" t="n">
         <v>1</v>
@@ -7576,6 +7903,15 @@
         <v>1</v>
       </c>
       <c r="AW27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ27" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7678,49 +8014,52 @@
         <v>78</v>
       </c>
       <c r="AF28" s="14" t="n"/>
-      <c r="AG28" s="14" t="n">
-        <v>68</v>
-      </c>
+      <c r="AG28" s="14" t="n"/>
       <c r="AH28" s="14" t="n"/>
       <c r="AI28" s="14" t="n"/>
       <c r="AJ28" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="AK28" s="14" t="n"/>
+      <c r="AL28" s="14" t="n"/>
+      <c r="AM28" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="AK28" s="7" t="n"/>
-      <c r="AL28" s="7" t="n">
+      <c r="AN28" s="7" t="n"/>
+      <c r="AO28" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="AM28" s="7" t="n">
+      <c r="AP28" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="AN28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP28" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AT28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ28" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7824,58 +8163,61 @@
       <c r="AE29" s="14" t="n">
         <v>83.55</v>
       </c>
-      <c r="AF29" s="14" t="n">
+      <c r="AF29" s="14" t="n"/>
+      <c r="AG29" s="14" t="n"/>
+      <c r="AH29" s="14" t="n"/>
+      <c r="AI29" s="14" t="n">
         <v>43.9</v>
       </c>
-      <c r="AG29" s="14" t="n">
+      <c r="AJ29" s="14" t="n">
         <v>39.9</v>
       </c>
-      <c r="AH29" s="14" t="n">
+      <c r="AK29" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="AI29" s="14" t="n">
+      <c r="AL29" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="AJ29" s="14" t="n">
+      <c r="AM29" s="14" t="n">
         <v>37.9</v>
       </c>
-      <c r="AK29" s="7" t="n">
+      <c r="AN29" s="7" t="n">
         <v>225</v>
       </c>
-      <c r="AL29" s="7" t="n">
+      <c r="AO29" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="AM29" s="7" t="n">
+      <c r="AP29" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="AN29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP29" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ29" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7975,48 +8317,42 @@
       <c r="AE30" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="AF30" s="14" t="n">
+      <c r="AF30" s="14" t="n"/>
+      <c r="AG30" s="14" t="n"/>
+      <c r="AH30" s="14" t="n"/>
+      <c r="AI30" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AG30" s="14" t="n">
+      <c r="AJ30" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="AH30" s="14" t="n">
+      <c r="AK30" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="AI30" s="14" t="n">
+      <c r="AL30" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AJ30" s="14" t="n">
+      <c r="AM30" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="AK30" s="7" t="n"/>
-      <c r="AL30" s="7" t="n">
+      <c r="AN30" s="7" t="n"/>
+      <c r="AO30" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="AM30" s="7" t="n">
+      <c r="AP30" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AN30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP30" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AS30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU30" s="4" t="n">
         <v>1</v>
@@ -8025,6 +8361,15 @@
         <v>1</v>
       </c>
       <c r="AW30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ30" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8128,58 +8473,61 @@
       <c r="AE31" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="AF31" s="14" t="n">
+      <c r="AF31" s="14" t="n"/>
+      <c r="AG31" s="14" t="n"/>
+      <c r="AH31" s="14" t="n"/>
+      <c r="AI31" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="AG31" s="14" t="n">
+      <c r="AJ31" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="AH31" s="14" t="n">
+      <c r="AK31" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="AI31" s="14" t="n">
+      <c r="AL31" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AJ31" s="14" t="n">
+      <c r="AM31" s="14" t="n">
         <v>21.5</v>
       </c>
-      <c r="AK31" s="7" t="n">
+      <c r="AN31" s="7" t="n">
         <v>239</v>
       </c>
-      <c r="AL31" s="7" t="n">
+      <c r="AO31" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="AM31" s="7" t="n">
+      <c r="AP31" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AN31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ31" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8283,58 +8631,61 @@
       <c r="AE32" s="14" t="n">
         <v>52.5</v>
       </c>
-      <c r="AF32" s="14" t="n">
+      <c r="AF32" s="14" t="n"/>
+      <c r="AG32" s="14" t="n"/>
+      <c r="AH32" s="14" t="n"/>
+      <c r="AI32" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="AG32" s="14" t="n">
+      <c r="AJ32" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="AH32" s="14" t="n">
+      <c r="AK32" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AI32" s="14" t="n">
+      <c r="AL32" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AJ32" s="14" t="n">
+      <c r="AM32" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AK32" s="7" t="n">
+      <c r="AN32" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="AL32" s="7" t="n">
+      <c r="AO32" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AM32" s="7" t="n">
+      <c r="AP32" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="AN32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ32" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8436,42 +8787,36 @@
       <c r="AE33" s="14" t="n">
         <v>76.8</v>
       </c>
-      <c r="AF33" s="14" t="n">
+      <c r="AF33" s="14" t="n"/>
+      <c r="AG33" s="14" t="n"/>
+      <c r="AH33" s="14" t="n"/>
+      <c r="AI33" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="AG33" s="14" t="n">
+      <c r="AJ33" s="14" t="n">
         <v>24.9</v>
       </c>
-      <c r="AH33" s="14" t="n"/>
-      <c r="AI33" s="14" t="n"/>
-      <c r="AJ33" s="14" t="n"/>
-      <c r="AK33" s="7" t="n"/>
-      <c r="AL33" s="7" t="n">
+      <c r="AK33" s="14" t="n"/>
+      <c r="AL33" s="14" t="n"/>
+      <c r="AM33" s="14" t="n"/>
+      <c r="AN33" s="7" t="n"/>
+      <c r="AO33" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="AM33" s="7" t="n">
+      <c r="AP33" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="AN33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP33" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AS33" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT33" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU33" s="4" t="n">
         <v>1</v>
@@ -8480,6 +8825,15 @@
         <v>1</v>
       </c>
       <c r="AW33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ33" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8576,31 +8930,25 @@
       <c r="AH34" s="14" t="n"/>
       <c r="AI34" s="14" t="n"/>
       <c r="AJ34" s="14" t="n"/>
-      <c r="AK34" s="7" t="n"/>
-      <c r="AL34" s="7" t="n">
+      <c r="AK34" s="14" t="n"/>
+      <c r="AL34" s="14" t="n"/>
+      <c r="AM34" s="14" t="n"/>
+      <c r="AN34" s="7" t="n"/>
+      <c r="AO34" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="AM34" s="7" t="n">
+      <c r="AP34" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="AN34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="4" t="n"/>
       <c r="AQ34" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS34" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS34" s="4" t="n"/>
       <c r="AT34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU34" s="4" t="n">
         <v>1</v>
@@ -8609,6 +8957,15 @@
         <v>1</v>
       </c>
       <c r="AW34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ34" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8710,46 +9067,40 @@
       <c r="AE35" s="14" t="n">
         <v>41.9</v>
       </c>
-      <c r="AF35" s="14" t="n">
+      <c r="AF35" s="14" t="n"/>
+      <c r="AG35" s="14" t="n"/>
+      <c r="AH35" s="14" t="n"/>
+      <c r="AI35" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AG35" s="14" t="n">
+      <c r="AJ35" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="AH35" s="14" t="n">
+      <c r="AK35" s="14" t="n">
         <v>6.5</v>
       </c>
-      <c r="AI35" s="14" t="n">
+      <c r="AL35" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AJ35" s="14" t="n"/>
-      <c r="AK35" s="7" t="n"/>
-      <c r="AL35" s="7" t="n">
+      <c r="AM35" s="14" t="n"/>
+      <c r="AN35" s="7" t="n"/>
+      <c r="AO35" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="AM35" s="7" t="n">
+      <c r="AP35" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="AN35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP35" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ35" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AS35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU35" s="4" t="n">
         <v>1</v>
@@ -8758,6 +9109,15 @@
         <v>1</v>
       </c>
       <c r="AW35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ35" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8852,39 +9212,33 @@
       <c r="AF36" s="14" t="n"/>
       <c r="AG36" s="14" t="n"/>
       <c r="AH36" s="14" t="n"/>
-      <c r="AI36" s="14" t="n">
+      <c r="AI36" s="14" t="n"/>
+      <c r="AJ36" s="14" t="n"/>
+      <c r="AK36" s="14" t="n"/>
+      <c r="AL36" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AJ36" s="14" t="n"/>
-      <c r="AK36" s="7" t="n">
+      <c r="AM36" s="14" t="n"/>
+      <c r="AN36" s="7" t="n">
         <v>331</v>
       </c>
-      <c r="AL36" s="7" t="n">
+      <c r="AO36" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AM36" s="7" t="n">
+      <c r="AP36" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AN36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP36" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ36" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR36" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AS36" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT36" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU36" s="4" t="n">
         <v>1</v>
@@ -8893,6 +9247,15 @@
         <v>1</v>
       </c>
       <c r="AW36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ36" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8993,57 +9356,66 @@
         <v>92.5</v>
       </c>
       <c r="AF37" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="AG37" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="AH37" s="14" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="AI37" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="AG37" s="14" t="n">
+      <c r="AJ37" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="AH37" s="14" t="n">
+      <c r="AK37" s="14" t="n">
         <v>18.5</v>
       </c>
-      <c r="AI37" s="14" t="n">
+      <c r="AL37" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="AJ37" s="14" t="n">
+      <c r="AM37" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="AK37" s="7" t="n">
+      <c r="AN37" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="AL37" s="7" t="n">
+      <c r="AO37" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="AM37" s="7" t="n">
+      <c r="AP37" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="AN37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP37" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ37" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9140,41 +9512,44 @@
       <c r="AH38" s="14" t="n"/>
       <c r="AI38" s="14" t="n"/>
       <c r="AJ38" s="14" t="n"/>
-      <c r="AK38" s="7" t="n">
+      <c r="AK38" s="14" t="n"/>
+      <c r="AL38" s="14" t="n"/>
+      <c r="AM38" s="14" t="n"/>
+      <c r="AN38" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="AL38" s="7" t="n">
+      <c r="AO38" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="AM38" s="7" t="n">
+      <c r="AP38" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="AN38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" s="4" t="n"/>
       <c r="AQ38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AS38" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS38" s="4" t="n"/>
       <c r="AT38" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU38" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV38" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ38" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9271,33 +9646,27 @@
       <c r="AH39" s="14" t="n"/>
       <c r="AI39" s="14" t="n"/>
       <c r="AJ39" s="14" t="n"/>
-      <c r="AK39" s="7" t="n">
+      <c r="AK39" s="14" t="n"/>
+      <c r="AL39" s="14" t="n"/>
+      <c r="AM39" s="14" t="n"/>
+      <c r="AN39" s="7" t="n">
         <v>227</v>
       </c>
-      <c r="AL39" s="7" t="n">
+      <c r="AO39" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="AM39" s="7" t="n">
+      <c r="AP39" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AN39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS39" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS39" s="4" t="n"/>
       <c r="AT39" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU39" s="4" t="n">
         <v>1</v>
@@ -9306,6 +9675,15 @@
         <v>1</v>
       </c>
       <c r="AW39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ39" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9405,56 +9783,59 @@
       <c r="AE40" s="14" t="n">
         <v>53.5</v>
       </c>
-      <c r="AF40" s="14" t="n">
+      <c r="AF40" s="14" t="n"/>
+      <c r="AG40" s="14" t="n"/>
+      <c r="AH40" s="14" t="n"/>
+      <c r="AI40" s="14" t="n">
         <v>38.9</v>
       </c>
-      <c r="AG40" s="14" t="n">
+      <c r="AJ40" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="AH40" s="14" t="n">
+      <c r="AK40" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="AI40" s="14" t="n">
+      <c r="AL40" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="AJ40" s="14" t="n"/>
-      <c r="AK40" s="7" t="n">
+      <c r="AM40" s="14" t="n"/>
+      <c r="AN40" s="7" t="n">
         <v>633</v>
       </c>
-      <c r="AL40" s="7" t="n">
+      <c r="AO40" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="AM40" s="7" t="n">
+      <c r="AP40" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="AN40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP40" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS40" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT40" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU40" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV40" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ40" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9559,34 +9940,28 @@
         <v>34.5</v>
       </c>
       <c r="AF41" s="14" t="n"/>
-      <c r="AG41" s="14" t="n">
+      <c r="AG41" s="14" t="n"/>
+      <c r="AH41" s="14" t="n"/>
+      <c r="AI41" s="14" t="n"/>
+      <c r="AJ41" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="AH41" s="14" t="n">
+      <c r="AK41" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="AI41" s="14" t="n">
+      <c r="AL41" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="AJ41" s="14" t="n"/>
-      <c r="AK41" s="7" t="n">
+      <c r="AM41" s="14" t="n"/>
+      <c r="AN41" s="7" t="n">
         <v>438</v>
       </c>
-      <c r="AL41" s="7" t="n">
+      <c r="AO41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="AM41" s="7" t="n">
+      <c r="AP41" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="AN41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP41" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ41" s="4" t="n">
         <v>1</v>
       </c>
@@ -9594,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="AS41" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT41" s="4" t="n">
         <v>1</v>
@@ -9606,6 +9981,15 @@
         <v>1</v>
       </c>
       <c r="AW41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ41" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9697,48 +10081,51 @@
       <c r="AC42" s="14" t="n"/>
       <c r="AD42" s="14" t="n"/>
       <c r="AE42" s="14" t="n"/>
-      <c r="AF42" s="14" t="n">
+      <c r="AF42" s="14" t="n"/>
+      <c r="AG42" s="14" t="n"/>
+      <c r="AH42" s="14" t="n"/>
+      <c r="AI42" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="AG42" s="14" t="n">
+      <c r="AJ42" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="AH42" s="14" t="n"/>
-      <c r="AI42" s="14" t="n"/>
-      <c r="AJ42" s="14" t="n"/>
-      <c r="AK42" s="7" t="n">
+      <c r="AK42" s="14" t="n"/>
+      <c r="AL42" s="14" t="n"/>
+      <c r="AM42" s="14" t="n"/>
+      <c r="AN42" s="7" t="n">
         <v>221</v>
       </c>
-      <c r="AL42" s="7" t="n"/>
-      <c r="AM42" s="7" t="n"/>
-      <c r="AN42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP42" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO42" s="7" t="n"/>
+      <c r="AP42" s="7" t="n"/>
       <c r="AQ42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ42" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9835,29 +10222,23 @@
       <c r="AH43" s="14" t="n"/>
       <c r="AI43" s="14" t="n"/>
       <c r="AJ43" s="14" t="n"/>
-      <c r="AK43" s="7" t="n"/>
-      <c r="AL43" s="7" t="n">
+      <c r="AK43" s="14" t="n"/>
+      <c r="AL43" s="14" t="n"/>
+      <c r="AM43" s="14" t="n"/>
+      <c r="AN43" s="7" t="n"/>
+      <c r="AO43" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="AM43" s="7" t="n">
+      <c r="AP43" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AN43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" s="4" t="n"/>
       <c r="AQ43" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AR43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS43" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS43" s="4" t="n"/>
       <c r="AT43" s="4" t="n">
         <v>1</v>
       </c>
@@ -9868,6 +10249,15 @@
         <v>1</v>
       </c>
       <c r="AW43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ43" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9968,51 +10358,54 @@
         <v>30.25</v>
       </c>
       <c r="AF44" s="14" t="n"/>
-      <c r="AG44" s="14" t="n">
+      <c r="AG44" s="14" t="n"/>
+      <c r="AH44" s="14" t="n"/>
+      <c r="AI44" s="14" t="n"/>
+      <c r="AJ44" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="AH44" s="14" t="n">
+      <c r="AK44" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="AI44" s="14" t="n">
+      <c r="AL44" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="AJ44" s="14" t="n"/>
-      <c r="AK44" s="7" t="n"/>
-      <c r="AL44" s="7" t="n">
+      <c r="AM44" s="14" t="n"/>
+      <c r="AN44" s="7" t="n"/>
+      <c r="AO44" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AM44" s="7" t="n">
+      <c r="AP44" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AN44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP44" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AT44" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU44" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV44" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ44" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10115,47 +10508,50 @@
       <c r="AF45" s="14" t="n"/>
       <c r="AG45" s="14" t="n"/>
       <c r="AH45" s="14" t="n"/>
-      <c r="AI45" s="14" t="n">
+      <c r="AI45" s="14" t="n"/>
+      <c r="AJ45" s="14" t="n"/>
+      <c r="AK45" s="14" t="n"/>
+      <c r="AL45" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="AJ45" s="14" t="n"/>
-      <c r="AK45" s="7" t="n">
+      <c r="AM45" s="14" t="n"/>
+      <c r="AN45" s="7" t="n">
         <v>270</v>
       </c>
-      <c r="AL45" s="7" t="n">
+      <c r="AO45" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="AM45" s="7" t="n">
+      <c r="AP45" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AN45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP45" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS45" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT45" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU45" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ45" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10257,37 +10653,31 @@
       <c r="AE46" s="14" t="n">
         <v>58</v>
       </c>
-      <c r="AF46" s="14" t="n">
+      <c r="AF46" s="14" t="n"/>
+      <c r="AG46" s="14" t="n"/>
+      <c r="AH46" s="14" t="n"/>
+      <c r="AI46" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="AG46" s="14" t="n">
+      <c r="AJ46" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="AH46" s="14" t="n">
+      <c r="AK46" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="AI46" s="14" t="n">
+      <c r="AL46" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AJ46" s="14" t="n">
+      <c r="AM46" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="AK46" s="7" t="n"/>
-      <c r="AL46" s="7" t="n">
+      <c r="AN46" s="7" t="n"/>
+      <c r="AO46" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="AM46" s="7" t="n">
+      <c r="AP46" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="AN46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP46" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ46" s="4" t="n">
         <v>0</v>
       </c>
@@ -10295,10 +10685,10 @@
         <v>1</v>
       </c>
       <c r="AS46" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT46" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU46" s="4" t="n">
         <v>1</v>
@@ -10307,6 +10697,15 @@
         <v>1</v>
       </c>
       <c r="AW46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ46" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10401,33 +10800,27 @@
       <c r="AH47" s="14" t="n"/>
       <c r="AI47" s="14" t="n"/>
       <c r="AJ47" s="14" t="n"/>
-      <c r="AK47" s="7" t="n">
+      <c r="AK47" s="14" t="n"/>
+      <c r="AL47" s="14" t="n"/>
+      <c r="AM47" s="14" t="n"/>
+      <c r="AN47" s="7" t="n">
         <v>1010</v>
       </c>
-      <c r="AL47" s="7" t="n">
+      <c r="AO47" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="AM47" s="7" t="n">
+      <c r="AP47" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="AN47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" s="4" t="n"/>
       <c r="AQ47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS47" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS47" s="4" t="n"/>
       <c r="AT47" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU47" s="4" t="n">
         <v>1</v>
@@ -10436,6 +10829,15 @@
         <v>1</v>
       </c>
       <c r="AW47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ47" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10526,39 +10928,42 @@
       <c r="AH48" s="14" t="n"/>
       <c r="AI48" s="14" t="n"/>
       <c r="AJ48" s="14" t="n"/>
-      <c r="AK48" s="7" t="n"/>
-      <c r="AL48" s="7" t="n">
+      <c r="AK48" s="14" t="n"/>
+      <c r="AL48" s="14" t="n"/>
+      <c r="AM48" s="14" t="n"/>
+      <c r="AN48" s="7" t="n"/>
+      <c r="AO48" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AM48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" s="4" t="n"/>
+      <c r="AP48" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AR48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AS48" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU48" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV48" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AW48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ48" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10649,29 +11054,23 @@
       <c r="AH49" s="14" t="n"/>
       <c r="AI49" s="14" t="n"/>
       <c r="AJ49" s="14" t="n"/>
-      <c r="AK49" s="7" t="n"/>
-      <c r="AL49" s="7" t="n">
+      <c r="AK49" s="14" t="n"/>
+      <c r="AL49" s="14" t="n"/>
+      <c r="AM49" s="14" t="n"/>
+      <c r="AN49" s="7" t="n"/>
+      <c r="AO49" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="AM49" s="7" t="n">
+      <c r="AP49" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AN49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" s="4" t="n"/>
       <c r="AQ49" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS49" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS49" s="4" t="n"/>
       <c r="AT49" s="4" t="n">
         <v>1</v>
       </c>
@@ -10682,6 +11081,15 @@
         <v>1</v>
       </c>
       <c r="AW49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ49" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10776,29 +11184,23 @@
       <c r="AH50" s="14" t="n"/>
       <c r="AI50" s="14" t="n"/>
       <c r="AJ50" s="14" t="n"/>
-      <c r="AK50" s="7" t="n"/>
-      <c r="AL50" s="7" t="n">
+      <c r="AK50" s="14" t="n"/>
+      <c r="AL50" s="14" t="n"/>
+      <c r="AM50" s="14" t="n"/>
+      <c r="AN50" s="7" t="n"/>
+      <c r="AO50" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="AM50" s="7" t="n">
+      <c r="AP50" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AN50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" s="4" t="n"/>
       <c r="AQ50" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS50" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS50" s="4" t="n"/>
       <c r="AT50" s="4" t="n">
         <v>1</v>
       </c>
@@ -10809,6 +11211,15 @@
         <v>1</v>
       </c>
       <c r="AW50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ50" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10902,31 +11313,25 @@
       <c r="AC51" s="14" t="n"/>
       <c r="AD51" s="14" t="n"/>
       <c r="AE51" s="14" t="n"/>
-      <c r="AF51" s="14" t="n">
+      <c r="AF51" s="14" t="n"/>
+      <c r="AG51" s="14" t="n"/>
+      <c r="AH51" s="14" t="n"/>
+      <c r="AI51" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="AG51" s="14" t="n">
+      <c r="AJ51" s="14" t="n">
         <v>54</v>
       </c>
-      <c r="AH51" s="14" t="n"/>
-      <c r="AI51" s="14" t="n"/>
-      <c r="AJ51" s="14" t="n"/>
-      <c r="AK51" s="7" t="n"/>
-      <c r="AL51" s="7" t="n">
+      <c r="AK51" s="14" t="n"/>
+      <c r="AL51" s="14" t="n"/>
+      <c r="AM51" s="14" t="n"/>
+      <c r="AN51" s="7" t="n"/>
+      <c r="AO51" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="AM51" s="7" t="n">
+      <c r="AP51" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AN51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP51" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ51" s="4" t="n">
         <v>0</v>
       </c>
@@ -10934,10 +11339,10 @@
         <v>1</v>
       </c>
       <c r="AS51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU51" s="4" t="n">
         <v>1</v>
@@ -10946,6 +11351,15 @@
         <v>1</v>
       </c>
       <c r="AW51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ51" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11041,41 +11455,35 @@
       <c r="AE52" s="14" t="n">
         <v>37.6</v>
       </c>
-      <c r="AF52" s="14" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="AF52" s="14" t="n"/>
       <c r="AG52" s="14" t="n"/>
       <c r="AH52" s="14" t="n"/>
       <c r="AI52" s="14" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AJ52" s="14" t="n"/>
+      <c r="AK52" s="14" t="n"/>
+      <c r="AL52" s="14" t="n">
         <v>6.5</v>
       </c>
-      <c r="AJ52" s="14" t="n"/>
-      <c r="AK52" s="7" t="n">
+      <c r="AM52" s="14" t="n"/>
+      <c r="AN52" s="7" t="n">
         <v>245</v>
       </c>
-      <c r="AL52" s="7" t="n">
+      <c r="AO52" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AM52" s="7" t="n">
+      <c r="AP52" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="AN52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP52" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ52" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR52" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AS52" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT52" s="4" t="n">
         <v>1</v>
@@ -11087,6 +11495,15 @@
         <v>1</v>
       </c>
       <c r="AW52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ52" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11188,45 +11605,39 @@
       <c r="AE53" s="14" t="n">
         <v>67.67</v>
       </c>
-      <c r="AF53" s="14" t="n">
+      <c r="AF53" s="14" t="n"/>
+      <c r="AG53" s="14" t="n"/>
+      <c r="AH53" s="14" t="n"/>
+      <c r="AI53" s="14" t="n">
         <v>29.9</v>
       </c>
-      <c r="AG53" s="14" t="n">
+      <c r="AJ53" s="14" t="n">
         <v>29.2</v>
       </c>
-      <c r="AH53" s="14" t="n">
+      <c r="AK53" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="AI53" s="14" t="n">
+      <c r="AL53" s="14" t="n">
         <v>6.75</v>
       </c>
-      <c r="AJ53" s="14" t="n">
+      <c r="AM53" s="14" t="n">
         <v>20.9</v>
       </c>
-      <c r="AK53" s="7" t="n"/>
-      <c r="AL53" s="7" t="n">
+      <c r="AN53" s="7" t="n"/>
+      <c r="AO53" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="AM53" s="7" t="n">
+      <c r="AP53" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="AN53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP53" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ53" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR53" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AS53" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT53" s="4" t="n">
         <v>1</v>
@@ -11238,6 +11649,15 @@
         <v>1</v>
       </c>
       <c r="AW53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ53" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11339,45 +11759,39 @@
       <c r="AE54" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="AF54" s="14" t="n">
+      <c r="AF54" s="14" t="n"/>
+      <c r="AG54" s="14" t="n"/>
+      <c r="AH54" s="14" t="n"/>
+      <c r="AI54" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="AG54" s="14" t="n">
+      <c r="AJ54" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="AH54" s="14" t="n">
+      <c r="AK54" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="AI54" s="14" t="n">
+      <c r="AL54" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="AJ54" s="14" t="n">
+      <c r="AM54" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="AK54" s="7" t="n"/>
-      <c r="AL54" s="7" t="n">
+      <c r="AN54" s="7" t="n"/>
+      <c r="AO54" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="AM54" s="7" t="n">
+      <c r="AP54" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="AN54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP54" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ54" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR54" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AS54" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT54" s="4" t="n">
         <v>1</v>
@@ -11389,6 +11803,15 @@
         <v>1</v>
       </c>
       <c r="AW54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ54" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11487,32 +11910,26 @@
       <c r="AF55" s="14" t="n"/>
       <c r="AG55" s="14" t="n"/>
       <c r="AH55" s="14" t="n"/>
-      <c r="AI55" s="14" t="n">
+      <c r="AI55" s="14" t="n"/>
+      <c r="AJ55" s="14" t="n"/>
+      <c r="AK55" s="14" t="n"/>
+      <c r="AL55" s="14" t="n">
         <v>7.5</v>
       </c>
-      <c r="AJ55" s="14" t="n"/>
-      <c r="AK55" s="7" t="n">
+      <c r="AM55" s="14" t="n"/>
+      <c r="AN55" s="7" t="n">
         <v>287</v>
       </c>
-      <c r="AL55" s="7" t="n"/>
-      <c r="AM55" s="7" t="n"/>
-      <c r="AN55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP55" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO55" s="7" t="n"/>
+      <c r="AP55" s="7" t="n"/>
       <c r="AQ55" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR55" s="4" t="n">
         <v>1</v>
       </c>
       <c r="AS55" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT55" s="4" t="n">
         <v>1</v>
@@ -11524,11 +11941,20 @@
         <v>1</v>
       </c>
       <c r="AW55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ55" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AW55"/>
+  <autoFilter ref="A1:AZ55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11539,7 +11965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12101,7 +12527,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>cesta_baixa</t>
+          <t>consumo_baixa</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -12111,7 +12537,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível baixo (P25)</t>
+          <t>Consumo por pessoa (bebida + entrada ou prato), nível baixo (P25)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -12123,7 +12549,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>cesta_mediana</t>
+          <t>consumo_mediana</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -12133,7 +12559,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível mediano</t>
+          <t>Consumo por pessoa (bebida + entrada ou prato), nível mediano</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -12145,7 +12571,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>cesta_alta</t>
+          <t>consumo_alta</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -12155,7 +12581,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Cesta por pessoa, nível alto (P75)</t>
+          <t>Consumo por pessoa (bebida + entrada ou prato), nível alto (P75)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -12167,7 +12593,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>hamburguer_mediana</t>
+          <t>cesta_baixa</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12177,7 +12603,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Hambúrguer, mediana</t>
+          <t>Cesta completa (consumo + couvert encontrado), nível baixo (P25)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -12189,7 +12615,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>batata_mediana</t>
+          <t>cesta_mediana</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -12199,7 +12625,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Batata, mediana</t>
+          <t>Cesta completa (consumo + couvert encontrado), nível mediano</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -12211,7 +12637,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>cerveja_mediana</t>
+          <t>cesta_alta</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -12221,7 +12647,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Cerveja, mediana</t>
+          <t>Cesta completa (consumo + couvert encontrado), nível alto (P75)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -12233,7 +12659,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>refrigerante_mediana</t>
+          <t>hamburguer_mediana</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -12243,7 +12669,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Refrigerante, mediana</t>
+          <t>Hambúrguer, mediana</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -12255,7 +12681,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>drinks_mediana</t>
+          <t>batata_mediana</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -12265,7 +12691,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Drinks, mediana</t>
+          <t>Batata, mediana</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -12277,139 +12703,139 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>titulos_acervo</t>
+          <t>cerveja_mediana</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Acervo</t>
+          <t>Cardápio</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Títulos no acervo publicado</t>
+          <t>Cerveja, mediana</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>R$</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>avaliacoes_b2</t>
+          <t>refrigerante_mediana</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Cardápio</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Avaliações no recorte do B2 (até '3 meses atrás')</t>
+          <t>Refrigerante, mediana</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>avaliações</t>
+          <t>R$</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>avaliacoes_b2_com_texto</t>
+          <t>drinks_mediana</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Cardápio</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Dessas, com texto</t>
+          <t>Drinks, mediana</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>avaliações</t>
+          <t>R$</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>tem_metro_1000m</t>
+          <t>titulos_acervo</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Proporção</t>
+          <t>Acervo</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Com estação de metrô até 1000 m (1 = sim, 0 = não)</t>
+          <t>Títulos no acervo publicado</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>0 ou 1</t>
+          <t>jogos</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>tem_cardapio</t>
+          <t>avaliacoes_b2</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Proporção</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Com cardápio transcrito (1 = sim, 0 = não)</t>
+          <t>Avaliações no recorte do B2 (até '3 meses atrás')</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>0 ou 1</t>
+          <t>avaliações</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>cobra_couvert</t>
+          <t>avaliacoes_b2_com_texto</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Proporção</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Cobra couvert ou taxa de jogo (entre as com cardápio) (1 = sim, 0 = não)</t>
+          <t>Dessas, com texto</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0 ou 1</t>
+          <t>avaliações</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>abre_segunda</t>
+          <t>tem_metro_1000m</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -12419,7 +12845,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Abre segunda (1 = sim, 0 = não)</t>
+          <t>Com estação de metrô até 1000 m (1 = sim, 0 = não)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -12431,7 +12857,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>abre_terca</t>
+          <t>tem_cardapio</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -12441,7 +12867,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Abre terça (1 = sim, 0 = não)</t>
+          <t>Com cardápio transcrito (1 = sim, 0 = não)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -12453,7 +12879,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>abre_quarta</t>
+          <t>cobra_couvert</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -12463,7 +12889,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Abre quarta (1 = sim, 0 = não)</t>
+          <t>Cobra couvert ou taxa de jogo (entre as com cardápio) (1 = sim, 0 = não)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -12475,7 +12901,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>abre_quinta</t>
+          <t>abre_segunda</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -12485,7 +12911,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Abre quinta (1 = sim, 0 = não)</t>
+          <t>Abre segunda (1 = sim, 0 = não)</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -12497,7 +12923,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>abre_sexta</t>
+          <t>abre_terca</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -12507,7 +12933,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Abre sexta (1 = sim, 0 = não)</t>
+          <t>Abre terça (1 = sim, 0 = não)</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -12519,7 +12945,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>abre_sabado</t>
+          <t>abre_quarta</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -12529,7 +12955,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Abre sábado (1 = sim, 0 = não)</t>
+          <t>Abre quarta (1 = sim, 0 = não)</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -12541,7 +12967,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>abre_domingo</t>
+          <t>abre_quinta</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -12551,7 +12977,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Abre domingo (1 = sim, 0 = não)</t>
+          <t>Abre quinta (1 = sim, 0 = não)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -12563,49 +12989,115 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>regiao</t>
+          <t>abre_sexta</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Identificação</t>
+          <t>Proporção</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Região do Brasil da capital da metrópole (IBGE)</t>
+          <t>Abre sexta (1 = sim, 0 = não)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 ou 1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
+          <t>abre_sabado</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Proporção</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Abre sábado (1 = sim, 0 = não)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>0 ou 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>abre_domingo</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Proporção</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Abre domingo (1 = sim, 0 = não)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>0 ou 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>regiao</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Região do Brasil da capital da metrópole (IBGE)</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Regras</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Cada casa conta uma vez, na metrópole do endereço. Instagram de LudoCafé e Dominaria vazio (perfil coletado não é o da casa). Couvert só nas casas que cobram. Shoppings de porte só onde o porte foi buscado. Distâncias em linha reta (coletor de entorno). Desvio padrão amostral; quartis pelo método inclusivo.</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D48"/>
+  <autoFilter ref="A1:D51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_geral.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_geral.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="geral" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="frequencias" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dados" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dicionario" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="geral" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="frequencias" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="dados" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="dicionario" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'geral'!$A$1:$O$39</definedName>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Cobra couvert ou taxa de jogo (entre as com cardápio)</t>
+          <t>Couvert ou taxa de jogo encontrado (entre as com cardápio)</t>
         </is>
       </c>
       <c r="C28" s="4">
@@ -4193,12 +4193,8 @@
       <c r="M2" s="7" t="n">
         <v>768</v>
       </c>
-      <c r="N2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" s="5" t="n"/>
+      <c r="O2" s="5" t="n"/>
       <c r="P2" s="7" t="n">
         <v>305</v>
       </c>
@@ -4344,9 +4340,7 @@
       <c r="L3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="7" t="n">
-        <v>3099</v>
-      </c>
+      <c r="M3" s="7" t="n"/>
       <c r="N3" s="5" t="n"/>
       <c r="O3" s="5" t="n"/>
       <c r="P3" s="7" t="n">
@@ -4475,15 +4469,9 @@
       <c r="M4" s="7" t="n">
         <v>702</v>
       </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7" t="n">
-        <v>1505</v>
-      </c>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="7" t="n"/>
       <c r="Q4" s="7" t="n">
         <v>6058</v>
       </c>
@@ -4787,12 +4775,8 @@
       <c r="M6" s="7" t="n">
         <v>465</v>
       </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
       <c r="P6" s="7" t="n">
         <v>747</v>
       </c>
@@ -4946,15 +4930,9 @@
       <c r="L7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="7" t="n">
-        <v>6361</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
       <c r="P7" s="7" t="n">
         <v>162</v>
       </c>
@@ -5099,12 +5077,8 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="n"/>
-      <c r="N8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
       <c r="P8" s="7" t="n">
         <v>5</v>
       </c>
@@ -5230,9 +5204,7 @@
       <c r="L9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="7" t="n">
-        <v>3702</v>
-      </c>
+      <c r="M9" s="7" t="n"/>
       <c r="N9" s="5" t="n"/>
       <c r="O9" s="5" t="n"/>
       <c r="P9" s="7" t="n">
@@ -5496,18 +5468,10 @@
       <c r="L11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="7" t="n">
-        <v>5144</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7" t="n">
-        <v>1138</v>
-      </c>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="n">
         <v>27673</v>
       </c>
@@ -5653,12 +5617,8 @@
       <c r="M12" s="7" t="n">
         <v>387</v>
       </c>
-      <c r="N12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
       <c r="P12" s="7" t="n">
         <v>118</v>
       </c>
@@ -5809,12 +5769,8 @@
         <v>0</v>
       </c>
       <c r="M13" s="7" t="n"/>
-      <c r="N13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
       <c r="P13" s="7" t="n">
         <v>52</v>
       </c>
@@ -5843,7 +5799,7 @@
         <v>0.01614</v>
       </c>
       <c r="Y13" s="7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Z13" s="14" t="n">
         <v>25.5</v>
@@ -5855,7 +5811,7 @@
         <v>35</v>
       </c>
       <c r="AC13" s="14" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="AD13" s="14" t="n">
         <v>48</v>
@@ -5864,7 +5820,7 @@
         <v>54.5</v>
       </c>
       <c r="AF13" s="14" t="n">
-        <v>56.75</v>
+        <v>54.25</v>
       </c>
       <c r="AG13" s="14" t="n">
         <v>73.5</v>
@@ -5876,7 +5832,7 @@
         <v>40</v>
       </c>
       <c r="AJ13" s="14" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="AK13" s="14" t="n">
         <v>13</v>
@@ -5975,12 +5931,8 @@
       <c r="M14" s="7" t="n">
         <v>307</v>
       </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
       <c r="P14" s="7" t="n">
         <v>723</v>
       </c>
@@ -6120,15 +6072,9 @@
       <c r="L15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="7" t="n">
-        <v>1142</v>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>3</v>
-      </c>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
       <c r="P15" s="7" t="n">
         <v>105</v>
       </c>
@@ -6282,12 +6228,8 @@
       <c r="L16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="7" t="n">
-        <v>1201</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
       <c r="P16" s="7" t="n">
         <v>754</v>
@@ -6316,8 +6258,12 @@
       <c r="X16" s="12" t="n">
         <v>0.00134</v>
       </c>
-      <c r="Y16" s="7" t="n"/>
-      <c r="Z16" s="14" t="n"/>
+      <c r="Y16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="AA16" s="14" t="n"/>
       <c r="AB16" s="14" t="n"/>
       <c r="AC16" s="14" t="n"/>
@@ -6342,9 +6288,11 @@
         <v>0</v>
       </c>
       <c r="AR16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS16" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AT16" s="4" t="n">
         <v>0</v>
       </c>
@@ -6412,15 +6360,9 @@
       <c r="L17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="7" t="n">
-        <v>4984</v>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
       <c r="P17" s="7" t="n">
         <v>137</v>
       </c>
@@ -6568,15 +6510,9 @@
       <c r="L18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="7" t="n">
-        <v>3205</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
       <c r="P18" s="7" t="n">
         <v>391</v>
       </c>
@@ -6588,21 +6524,43 @@
       <c r="V18" s="7" t="n"/>
       <c r="W18" s="9" t="n"/>
       <c r="X18" s="12" t="n"/>
-      <c r="Y18" s="7" t="n"/>
-      <c r="Z18" s="14" t="n"/>
-      <c r="AA18" s="14" t="n"/>
-      <c r="AB18" s="14" t="n"/>
-      <c r="AC18" s="14" t="n"/>
-      <c r="AD18" s="14" t="n"/>
-      <c r="AE18" s="14" t="n"/>
-      <c r="AF18" s="14" t="n"/>
-      <c r="AG18" s="14" t="n"/>
-      <c r="AH18" s="14" t="n"/>
+      <c r="Y18" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z18" s="14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AA18" s="14" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AB18" s="14" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="AC18" s="14" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AD18" s="14" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AE18" s="14" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AF18" s="14" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="AG18" s="14" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="AH18" s="14" t="n">
+        <v>102.05</v>
+      </c>
       <c r="AI18" s="14" t="n"/>
       <c r="AJ18" s="14" t="n"/>
       <c r="AK18" s="14" t="n"/>
       <c r="AL18" s="14" t="n"/>
-      <c r="AM18" s="14" t="n"/>
+      <c r="AM18" s="14" t="n">
+        <v>38.9</v>
+      </c>
       <c r="AN18" s="7" t="n">
         <v>362</v>
       </c>
@@ -6616,9 +6574,11 @@
         <v>0</v>
       </c>
       <c r="AR18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS18" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AT18" s="4" t="n">
         <v>0</v>
       </c>
@@ -6686,9 +6646,7 @@
       <c r="L19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="7" t="n">
-        <v>2556</v>
-      </c>
+      <c r="M19" s="7" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="7" t="n">
@@ -6880,8 +6838,12 @@
       <c r="X20" s="12" t="n">
         <v>0.00223</v>
       </c>
-      <c r="Y20" s="7" t="n"/>
-      <c r="Z20" s="14" t="n"/>
+      <c r="Y20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z20" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="AA20" s="14" t="n"/>
       <c r="AB20" s="14" t="n"/>
       <c r="AC20" s="14" t="n"/>
@@ -6906,9 +6868,11 @@
         <v>1</v>
       </c>
       <c r="AR20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS20" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AT20" s="4" t="n">
         <v>0</v>
       </c>
@@ -6979,12 +6943,8 @@
       <c r="M21" s="7" t="n">
         <v>302</v>
       </c>
-      <c r="N21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
       <c r="P21" s="7" t="n">
         <v>576</v>
       </c>
@@ -7132,15 +7092,9 @@
       <c r="L22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="7" t="n">
-        <v>1216</v>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="M22" s="7" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
       <c r="P22" s="7" t="n">
         <v>312</v>
       </c>
@@ -7392,9 +7346,7 @@
       <c r="L24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="7" t="n">
-        <v>7638</v>
-      </c>
+      <c r="M24" s="7" t="n"/>
       <c r="N24" s="5" t="n"/>
       <c r="O24" s="5" t="n"/>
       <c r="P24" s="7" t="n">
@@ -7418,21 +7370,43 @@
         <v>207.62</v>
       </c>
       <c r="X24" s="12" t="n"/>
-      <c r="Y24" s="7" t="n"/>
+      <c r="Y24" s="7" t="n">
+        <v>75</v>
+      </c>
       <c r="Z24" s="14" t="n"/>
-      <c r="AA24" s="14" t="n"/>
-      <c r="AB24" s="14" t="n"/>
-      <c r="AC24" s="14" t="n"/>
-      <c r="AD24" s="14" t="n"/>
-      <c r="AE24" s="14" t="n"/>
+      <c r="AA24" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB24" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC24" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="AD24" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AE24" s="14" t="n">
+        <v>75.75</v>
+      </c>
       <c r="AF24" s="14" t="n"/>
       <c r="AG24" s="14" t="n"/>
       <c r="AH24" s="14" t="n"/>
-      <c r="AI24" s="14" t="n"/>
-      <c r="AJ24" s="14" t="n"/>
-      <c r="AK24" s="14" t="n"/>
-      <c r="AL24" s="14" t="n"/>
-      <c r="AM24" s="14" t="n"/>
+      <c r="AI24" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="AJ24" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK24" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL24" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM24" s="14" t="n">
+        <v>32</v>
+      </c>
       <c r="AN24" s="7" t="n">
         <v>1357</v>
       </c>
@@ -7442,9 +7416,11 @@
         <v>0</v>
       </c>
       <c r="AR24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS24" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="AT24" s="4" t="n">
         <v>0</v>
       </c>
@@ -7515,15 +7491,9 @@
       <c r="M25" s="7" t="n">
         <v>351</v>
       </c>
-      <c r="N25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="7" t="n">
-        <v>1796</v>
-      </c>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="n">
         <v>6682</v>
       </c>
@@ -7549,7 +7519,7 @@
         <v>0.00353</v>
       </c>
       <c r="Y25" s="7" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="Z25" s="14" t="n">
         <v>12.5</v>
@@ -7558,28 +7528,28 @@
         <v>11</v>
       </c>
       <c r="AB25" s="14" t="n">
-        <v>45</v>
+        <v>39.5</v>
       </c>
       <c r="AC25" s="14" t="n">
-        <v>46</v>
+        <v>43.25</v>
       </c>
       <c r="AD25" s="14" t="n">
-        <v>56</v>
+        <v>50.5</v>
       </c>
       <c r="AE25" s="14" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AF25" s="14" t="n">
-        <v>52.25</v>
+        <v>49.5</v>
       </c>
       <c r="AG25" s="14" t="n">
-        <v>68.5</v>
+        <v>63</v>
       </c>
       <c r="AH25" s="14" t="n">
-        <v>96.75</v>
+        <v>83.75</v>
       </c>
       <c r="AI25" s="14" t="n">
-        <v>52.5</v>
+        <v>42</v>
       </c>
       <c r="AJ25" s="14" t="n">
         <v>28.5</v>
@@ -7711,7 +7681,7 @@
         <v>0.00153</v>
       </c>
       <c r="Y26" s="7" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Z26" s="14" t="n"/>
       <c r="AA26" s="14" t="n">
@@ -7727,7 +7697,7 @@
         <v>60</v>
       </c>
       <c r="AE26" s="14" t="n">
-        <v>76</v>
+        <v>77.5</v>
       </c>
       <c r="AF26" s="14" t="n"/>
       <c r="AG26" s="14" t="n"/>
@@ -7739,7 +7709,7 @@
         <v>39</v>
       </c>
       <c r="AK26" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL26" s="14" t="n">
         <v>8</v>
@@ -7832,12 +7802,8 @@
       <c r="L27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="7" t="n">
-        <v>10228</v>
-      </c>
-      <c r="N27" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M27" s="7" t="n"/>
+      <c r="N27" s="5" t="n"/>
       <c r="O27" s="5" t="n"/>
       <c r="P27" s="7" t="n">
         <v>684</v>
@@ -7963,9 +7929,7 @@
       <c r="M28" s="7" t="n">
         <v>607</v>
       </c>
-      <c r="N28" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" s="5" t="n"/>
       <c r="O28" s="5" t="n"/>
       <c r="P28" s="7" t="n">
         <v>907</v>
@@ -8111,15 +8075,9 @@
       <c r="M29" s="7" t="n">
         <v>577</v>
       </c>
-      <c r="N29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="7" t="n">
-        <v>1006</v>
-      </c>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="7" t="n"/>
       <c r="Q29" s="7" t="n">
         <v>41545</v>
       </c>
@@ -8145,20 +8103,20 @@
         <v>0.00048</v>
       </c>
       <c r="Y29" s="7" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Z29" s="14" t="n"/>
       <c r="AA29" s="14" t="n">
-        <v>28.4</v>
+        <v>26.9</v>
       </c>
       <c r="AB29" s="14" t="n">
         <v>43.4</v>
       </c>
       <c r="AC29" s="14" t="n">
-        <v>55.57</v>
+        <v>54.15</v>
       </c>
       <c r="AD29" s="14" t="n">
-        <v>71.8</v>
+        <v>70.3</v>
       </c>
       <c r="AE29" s="14" t="n">
         <v>83.55</v>
@@ -8179,7 +8137,7 @@
         <v>9</v>
       </c>
       <c r="AM29" s="14" t="n">
-        <v>37.9</v>
+        <v>37.4</v>
       </c>
       <c r="AN29" s="7" t="n">
         <v>225</v>
@@ -8299,7 +8257,7 @@
         <v>0.00419</v>
       </c>
       <c r="Y30" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z30" s="14" t="n"/>
       <c r="AA30" s="14" t="n">
@@ -8309,7 +8267,7 @@
         <v>32</v>
       </c>
       <c r="AC30" s="14" t="n">
-        <v>47.75</v>
+        <v>47.5</v>
       </c>
       <c r="AD30" s="14" t="n">
         <v>60</v>
@@ -8324,7 +8282,7 @@
         <v>28</v>
       </c>
       <c r="AJ30" s="14" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="AK30" s="14" t="n">
         <v>22</v>
@@ -8418,15 +8376,9 @@
       <c r="L31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="7" t="n">
-        <v>7180</v>
-      </c>
-      <c r="N31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
       <c r="P31" s="7" t="n">
         <v>424</v>
       </c>
@@ -8576,18 +8528,10 @@
       <c r="L32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="7" t="n">
-        <v>16823</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="7" t="n">
-        <v>1993</v>
-      </c>
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="7" t="n"/>
       <c r="Q32" s="7" t="n">
         <v>2732</v>
       </c>
@@ -8737,9 +8681,7 @@
       <c r="M33" s="7" t="n">
         <v>687</v>
       </c>
-      <c r="N33" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N33" s="5" t="n"/>
       <c r="O33" s="5" t="n"/>
       <c r="P33" s="7" t="n">
         <v>835</v>
@@ -8885,15 +8827,9 @@
       <c r="M34" s="7" t="n">
         <v>628</v>
       </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="7" t="n">
-        <v>1205</v>
-      </c>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="7" t="n"/>
       <c r="Q34" s="7" t="n">
         <v>110000</v>
       </c>
@@ -8918,18 +8854,42 @@
       <c r="X34" s="12" t="n">
         <v>0.00117</v>
       </c>
-      <c r="Y34" s="7" t="n"/>
-      <c r="Z34" s="14" t="n"/>
-      <c r="AA34" s="14" t="n"/>
-      <c r="AB34" s="14" t="n"/>
-      <c r="AC34" s="14" t="n"/>
-      <c r="AD34" s="14" t="n"/>
-      <c r="AE34" s="14" t="n"/>
-      <c r="AF34" s="14" t="n"/>
-      <c r="AG34" s="14" t="n"/>
-      <c r="AH34" s="14" t="n"/>
-      <c r="AI34" s="14" t="n"/>
-      <c r="AJ34" s="14" t="n"/>
+      <c r="Y34" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z34" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA34" s="14" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="AB34" s="14" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="AC34" s="14" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="AD34" s="14" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AE34" s="14" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="AF34" s="14" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="AG34" s="14" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="AH34" s="14" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AI34" s="14" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="AJ34" s="14" t="n">
+        <v>26.7</v>
+      </c>
       <c r="AK34" s="14" t="n"/>
       <c r="AL34" s="14" t="n"/>
       <c r="AM34" s="14" t="n"/>
@@ -8944,9 +8904,11 @@
         <v>1</v>
       </c>
       <c r="AR34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS34" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AT34" s="4" t="n">
         <v>0</v>
       </c>
@@ -9017,9 +8979,7 @@
       <c r="M35" s="7" t="n">
         <v>435</v>
       </c>
-      <c r="N35" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" s="5" t="n"/>
       <c r="O35" s="5" t="n"/>
       <c r="P35" s="7" t="n">
         <v>818</v>
@@ -9467,15 +9427,9 @@
       <c r="M38" s="7" t="n">
         <v>820</v>
       </c>
-      <c r="N38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="7" t="n">
-        <v>1083</v>
-      </c>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="7" t="n"/>
       <c r="Q38" s="7" t="n">
         <v>8510</v>
       </c>
@@ -9601,15 +9555,9 @@
       <c r="M39" s="7" t="n">
         <v>566</v>
       </c>
-      <c r="N39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="7" t="n">
-        <v>1744</v>
-      </c>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="7" t="n"/>
       <c r="Q39" s="7" t="n">
         <v>23415</v>
       </c>
@@ -9732,9 +9680,7 @@
       <c r="L40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="7" t="n">
-        <v>4310</v>
-      </c>
+      <c r="M40" s="7" t="n"/>
       <c r="N40" s="5" t="n"/>
       <c r="O40" s="5" t="n"/>
       <c r="P40" s="7" t="n">
@@ -9765,23 +9711,23 @@
         <v>0.0064</v>
       </c>
       <c r="Y40" s="7" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="Z40" s="14" t="n"/>
       <c r="AA40" s="14" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AB40" s="14" t="n">
         <v>29</v>
       </c>
       <c r="AC40" s="14" t="n">
-        <v>18.18</v>
+        <v>17.9</v>
       </c>
       <c r="AD40" s="14" t="n">
-        <v>39.5</v>
+        <v>38</v>
       </c>
       <c r="AE40" s="14" t="n">
-        <v>53.5</v>
+        <v>52.72</v>
       </c>
       <c r="AF40" s="14" t="n"/>
       <c r="AG40" s="14" t="n"/>
@@ -9796,7 +9742,7 @@
         <v>13</v>
       </c>
       <c r="AL40" s="14" t="n">
-        <v>11</v>
+        <v>6.9</v>
       </c>
       <c r="AM40" s="14" t="n"/>
       <c r="AN40" s="7" t="n">
@@ -9887,12 +9833,8 @@
       <c r="M41" s="7" t="n">
         <v>563</v>
       </c>
-      <c r="N41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
       <c r="P41" s="7" t="n">
         <v>484</v>
       </c>
@@ -10038,15 +9980,9 @@
       <c r="L42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M42" s="7" t="n">
-        <v>1527</v>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="M42" s="7" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
       <c r="P42" s="7" t="n">
         <v>305</v>
       </c>
@@ -10071,7 +10007,7 @@
       </c>
       <c r="X42" s="12" t="n"/>
       <c r="Y42" s="7" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Z42" s="14" t="n"/>
       <c r="AA42" s="14" t="n"/>
@@ -10085,7 +10021,7 @@
       <c r="AG42" s="14" t="n"/>
       <c r="AH42" s="14" t="n"/>
       <c r="AI42" s="14" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AJ42" s="14" t="n">
         <v>35</v>
@@ -10177,15 +10113,9 @@
       <c r="M43" s="7" t="n">
         <v>364</v>
       </c>
-      <c r="N43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="7" t="n">
-        <v>1486</v>
-      </c>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="7" t="n"/>
       <c r="Q43" s="7" t="n">
         <v>34668</v>
       </c>
@@ -10307,9 +10237,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="7" t="n"/>
-      <c r="N44" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" s="5" t="n"/>
       <c r="O44" s="5" t="n"/>
       <c r="P44" s="7" t="n">
         <v>926</v>
@@ -10339,7 +10267,7 @@
         <v>0.00343</v>
       </c>
       <c r="Y44" s="7" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z44" s="14" t="n"/>
       <c r="AA44" s="14" t="n">
@@ -10455,9 +10383,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="7" t="n"/>
-      <c r="N45" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N45" s="5" t="n"/>
       <c r="O45" s="5" t="n"/>
       <c r="P45" s="7" t="n">
         <v>770</v>
@@ -10487,7 +10413,7 @@
         <v>0.00173</v>
       </c>
       <c r="Y45" s="7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z45" s="14" t="n"/>
       <c r="AA45" s="14" t="n">
@@ -10497,13 +10423,13 @@
         <v>12</v>
       </c>
       <c r="AC45" s="14" t="n">
-        <v>22</v>
+        <v>21.75</v>
       </c>
       <c r="AD45" s="14" t="n">
         <v>24</v>
       </c>
       <c r="AE45" s="14" t="n">
-        <v>34</v>
+        <v>28.5</v>
       </c>
       <c r="AF45" s="14" t="n"/>
       <c r="AG45" s="14" t="n"/>
@@ -10601,15 +10527,9 @@
         <v>0</v>
       </c>
       <c r="M46" s="7" t="n"/>
-      <c r="N46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="7" t="n">
-        <v>1175</v>
-      </c>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="7" t="n"/>
       <c r="Q46" s="7" t="n">
         <v>18698</v>
       </c>
@@ -10635,35 +10555,35 @@
         <v>0.00693</v>
       </c>
       <c r="Y46" s="7" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="Z46" s="14" t="n"/>
       <c r="AA46" s="14" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AB46" s="14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AC46" s="14" t="n">
-        <v>43</v>
+        <v>41.75</v>
       </c>
       <c r="AD46" s="14" t="n">
-        <v>47.5</v>
+        <v>44</v>
       </c>
       <c r="AE46" s="14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AF46" s="14" t="n"/>
       <c r="AG46" s="14" t="n"/>
       <c r="AH46" s="14" t="n"/>
       <c r="AI46" s="14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AJ46" s="14" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AK46" s="14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AL46" s="14" t="n">
         <v>8</v>
@@ -10755,15 +10675,9 @@
         <v>0</v>
       </c>
       <c r="M47" s="7" t="n"/>
-      <c r="N47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="7" t="n">
-        <v>1152</v>
-      </c>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="7" t="n"/>
       <c r="Q47" s="7" t="n">
         <v>25555</v>
       </c>
@@ -10788,8 +10702,12 @@
       <c r="X47" s="12" t="n">
         <v>0.01197</v>
       </c>
-      <c r="Y47" s="7" t="n"/>
-      <c r="Z47" s="14" t="n"/>
+      <c r="Y47" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z47" s="14" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA47" s="14" t="n"/>
       <c r="AB47" s="14" t="n"/>
       <c r="AC47" s="14" t="n"/>
@@ -10816,9 +10734,11 @@
         <v>0</v>
       </c>
       <c r="AR47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AS47" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AT47" s="4" t="n">
         <v>0</v>
       </c>
@@ -11139,12 +11059,8 @@
         <v>0</v>
       </c>
       <c r="M50" s="7" t="n"/>
-      <c r="N50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
       <c r="P50" s="7" t="n">
         <v>590</v>
       </c>
@@ -11269,12 +11185,8 @@
         <v>0</v>
       </c>
       <c r="M51" s="7" t="n"/>
-      <c r="N51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
       <c r="P51" s="7" t="n">
         <v>294</v>
       </c>
@@ -11303,7 +11215,7 @@
         <v>0.03043</v>
       </c>
       <c r="Y51" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z51" s="14" t="n"/>
       <c r="AA51" s="14" t="n"/>
@@ -11320,7 +11232,7 @@
         <v>36</v>
       </c>
       <c r="AJ51" s="14" t="n">
-        <v>54</v>
+        <v>44.5</v>
       </c>
       <c r="AK51" s="14" t="n"/>
       <c r="AL51" s="14" t="n"/>
@@ -11409,9 +11321,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="7" t="n"/>
-      <c r="N52" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N52" s="5" t="n"/>
       <c r="O52" s="5" t="n"/>
       <c r="P52" s="7" t="n">
         <v>834</v>
@@ -11437,7 +11347,7 @@
       <c r="W52" s="9" t="n"/>
       <c r="X52" s="12" t="n"/>
       <c r="Y52" s="7" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="Z52" s="14" t="n"/>
       <c r="AA52" s="14" t="n">
@@ -11447,13 +11357,13 @@
         <v>25.9</v>
       </c>
       <c r="AC52" s="14" t="n">
-        <v>28.4</v>
+        <v>30.4</v>
       </c>
       <c r="AD52" s="14" t="n">
         <v>32.7</v>
       </c>
       <c r="AE52" s="14" t="n">
-        <v>37.6</v>
+        <v>43.6</v>
       </c>
       <c r="AF52" s="14" t="n"/>
       <c r="AG52" s="14" t="n"/>
@@ -11553,15 +11463,9 @@
         <v>0</v>
       </c>
       <c r="M53" s="7" t="n"/>
-      <c r="N53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="7" t="n">
-        <v>1681</v>
-      </c>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="7" t="n"/>
       <c r="Q53" s="7" t="n">
         <v>87929</v>
       </c>
@@ -11587,23 +11491,23 @@
         <v>0.0023</v>
       </c>
       <c r="Y53" s="7" t="n">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="Z53" s="14" t="n"/>
       <c r="AA53" s="14" t="n">
         <v>17.9</v>
       </c>
       <c r="AB53" s="14" t="n">
-        <v>30.9</v>
+        <v>31.9</v>
       </c>
       <c r="AC53" s="14" t="n">
-        <v>34.9</v>
+        <v>35.55</v>
       </c>
       <c r="AD53" s="14" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
       <c r="AE53" s="14" t="n">
-        <v>67.67</v>
+        <v>71.42</v>
       </c>
       <c r="AF53" s="14" t="n"/>
       <c r="AG53" s="14" t="n"/>
@@ -11621,7 +11525,7 @@
         <v>6.75</v>
       </c>
       <c r="AM53" s="14" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="AN53" s="7" t="n"/>
       <c r="AO53" s="7" t="n">
@@ -11706,12 +11610,8 @@
       <c r="L54" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M54" s="7" t="n">
-        <v>1300</v>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M54" s="7" t="n"/>
+      <c r="N54" s="5" t="n"/>
       <c r="O54" s="5" t="n"/>
       <c r="P54" s="7" t="n">
         <v>591</v>
@@ -11741,7 +11641,7 @@
         <v>0.00084</v>
       </c>
       <c r="Y54" s="7" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Z54" s="14" t="n"/>
       <c r="AA54" s="14" t="n">
@@ -11751,13 +11651,13 @@
         <v>40</v>
       </c>
       <c r="AC54" s="14" t="n">
-        <v>52.75</v>
+        <v>55</v>
       </c>
       <c r="AD54" s="14" t="n">
         <v>65</v>
       </c>
       <c r="AE54" s="14" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF54" s="14" t="n"/>
       <c r="AG54" s="14" t="n"/>
@@ -11769,7 +11669,7 @@
         <v>28</v>
       </c>
       <c r="AK54" s="14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL54" s="14" t="n">
         <v>8</v>
@@ -11860,12 +11760,8 @@
       <c r="L55" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M55" s="7" t="n">
-        <v>15504</v>
-      </c>
-      <c r="N55" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="M55" s="7" t="n"/>
+      <c r="N55" s="5" t="n"/>
       <c r="O55" s="5" t="n"/>
       <c r="P55" s="7" t="n">
         <v>583</v>
@@ -12889,7 +12785,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Cobra couvert ou taxa de jogo (entre as com cardápio) (1 = sim, 0 = não)</t>
+          <t>Couvert ou taxa de jogo encontrado (entre as com cardápio) (1 = sim, 0 = não)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -13087,7 +12983,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Cada casa conta uma vez, na metrópole do endereço. Instagram de LudoCafé e Dominaria vazio (perfil coletado não é o da casa). Couvert só nas casas que cobram. Shoppings de porte só onde o porte foi buscado. Distâncias em linha reta (coletor de entorno). Desvio padrão amostral; quartis pelo método inclusivo.</t>
+          <t>Cada casa conta uma vez, na metrópole do endereço. Instagram de LudoCafé e Dominaria vazio (perfil coletado não é o da casa). Couvert só nas casas com couvert encontrado. Shoppings de porte só onde o porte foi buscado. Distâncias em linha reta (coletor de entorno). Desvio padrão amostral; quartis pelo método inclusivo.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">

--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_geral.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_geral.xlsx
@@ -4807,9 +4807,7 @@
       <c r="Y6" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="Z6" s="14" t="n">
-        <v>30</v>
-      </c>
+      <c r="Z6" s="14" t="n"/>
       <c r="AA6" s="14" t="n">
         <v>9</v>
       </c>
@@ -4817,7 +4815,7 @@
         <v>31</v>
       </c>
       <c r="AC6" s="14" t="n">
-        <v>34.5</v>
+        <v>34.75</v>
       </c>
       <c r="AD6" s="14" t="n">
         <v>40</v>
@@ -4825,15 +4823,9 @@
       <c r="AE6" s="14" t="n">
         <v>46.75</v>
       </c>
-      <c r="AF6" s="14" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="AG6" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AH6" s="14" t="n">
-        <v>76.75</v>
-      </c>
+      <c r="AF6" s="14" t="n"/>
+      <c r="AG6" s="14" t="n"/>
+      <c r="AH6" s="14" t="n"/>
       <c r="AI6" s="14" t="n"/>
       <c r="AJ6" s="14" t="n"/>
       <c r="AK6" s="14" t="n">
@@ -4861,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="AS6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT6" s="4" t="n">
         <v>0</v>
@@ -5497,9 +5489,11 @@
         <v>0.00249</v>
       </c>
       <c r="Y11" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z11" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="Z11" s="14" t="n"/>
       <c r="AA11" s="14" t="n">
         <v>12</v>
       </c>
@@ -5515,9 +5509,15 @@
       <c r="AE11" s="14" t="n">
         <v>37.5</v>
       </c>
-      <c r="AF11" s="14" t="n"/>
-      <c r="AG11" s="14" t="n"/>
-      <c r="AH11" s="14" t="n"/>
+      <c r="AF11" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="AG11" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="AH11" s="14" t="n">
+        <v>62.5</v>
+      </c>
       <c r="AI11" s="14" t="n">
         <v>34</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>1</v>
       </c>
       <c r="AS11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT11" s="4" t="n">
         <v>0</v>
@@ -5957,9 +5957,11 @@
       </c>
       <c r="X14" s="12" t="n"/>
       <c r="Y14" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="Z14" s="14" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="Z14" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="AA14" s="14" t="n">
         <v>20</v>
       </c>
@@ -5975,9 +5977,15 @@
       <c r="AE14" s="14" t="n">
         <v>71.5</v>
       </c>
-      <c r="AF14" s="14" t="n"/>
-      <c r="AG14" s="14" t="n"/>
-      <c r="AH14" s="14" t="n"/>
+      <c r="AF14" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="AG14" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="AH14" s="14" t="n">
+        <v>94</v>
+      </c>
       <c r="AI14" s="14" t="n">
         <v>42</v>
       </c>
@@ -6003,7 +6011,7 @@
         <v>1</v>
       </c>
       <c r="AS14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT14" s="4" t="n">
         <v>0</v>
@@ -6973,9 +6981,11 @@
         <v>0.01027</v>
       </c>
       <c r="Y21" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z21" s="14" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="Z21" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="AA21" s="14" t="n">
         <v>12</v>
       </c>
@@ -6991,9 +7001,15 @@
       <c r="AE21" s="14" t="n">
         <v>54.5</v>
       </c>
-      <c r="AF21" s="14" t="n"/>
-      <c r="AG21" s="14" t="n"/>
-      <c r="AH21" s="14" t="n"/>
+      <c r="AF21" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG21" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="AH21" s="14" t="n">
+        <v>74.5</v>
+      </c>
       <c r="AI21" s="14" t="n">
         <v>38</v>
       </c>
@@ -7023,7 +7039,7 @@
         <v>1</v>
       </c>
       <c r="AS21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT21" s="4" t="n">
         <v>0</v>
@@ -7371,9 +7387,11 @@
       </c>
       <c r="X24" s="12" t="n"/>
       <c r="Y24" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z24" s="14" t="n"/>
+        <v>77</v>
+      </c>
+      <c r="Z24" s="14" t="n">
+        <v>22.5</v>
+      </c>
       <c r="AA24" s="14" t="n">
         <v>25</v>
       </c>
@@ -7389,9 +7407,15 @@
       <c r="AE24" s="14" t="n">
         <v>75.75</v>
       </c>
-      <c r="AF24" s="14" t="n"/>
-      <c r="AG24" s="14" t="n"/>
-      <c r="AH24" s="14" t="n"/>
+      <c r="AF24" s="14" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="AG24" s="14" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="AH24" s="14" t="n">
+        <v>99.5</v>
+      </c>
       <c r="AI24" s="14" t="n">
         <v>49</v>
       </c>
@@ -7419,7 +7443,7 @@
         <v>1</v>
       </c>
       <c r="AS24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT24" s="4" t="n">
         <v>0</v>
@@ -8407,9 +8431,11 @@
         <v>0.03412</v>
       </c>
       <c r="Y31" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z31" s="14" t="n"/>
+        <v>73</v>
+      </c>
+      <c r="Z31" s="14" t="n">
+        <v>17.5</v>
+      </c>
       <c r="AA31" s="14" t="n">
         <v>18</v>
       </c>
@@ -8425,9 +8451,15 @@
       <c r="AE31" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="AF31" s="14" t="n"/>
-      <c r="AG31" s="14" t="n"/>
-      <c r="AH31" s="14" t="n"/>
+      <c r="AF31" s="14" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="AG31" s="14" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AH31" s="14" t="n">
+        <v>78.75</v>
+      </c>
       <c r="AI31" s="14" t="n">
         <v>29</v>
       </c>
@@ -8459,7 +8491,7 @@
         <v>1</v>
       </c>
       <c r="AS31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT31" s="4" t="n">
         <v>0</v>
@@ -8711,9 +8743,11 @@
         <v>0.00322</v>
       </c>
       <c r="Y33" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z33" s="14" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="Z33" s="14" t="n">
+        <v>40</v>
+      </c>
       <c r="AA33" s="14" t="n">
         <v>27.9</v>
       </c>
@@ -8729,9 +8763,15 @@
       <c r="AE33" s="14" t="n">
         <v>76.8</v>
       </c>
-      <c r="AF33" s="14" t="n"/>
-      <c r="AG33" s="14" t="n"/>
-      <c r="AH33" s="14" t="n"/>
+      <c r="AF33" s="14" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="AG33" s="14" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AH33" s="14" t="n">
+        <v>118.05</v>
+      </c>
       <c r="AI33" s="14" t="n">
         <v>38</v>
       </c>
@@ -8755,7 +8795,7 @@
         <v>1</v>
       </c>
       <c r="AS33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT33" s="4" t="n">
         <v>0</v>
@@ -9711,9 +9751,11 @@
         <v>0.0064</v>
       </c>
       <c r="Y40" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="Z40" s="14" t="n"/>
+        <v>56</v>
+      </c>
+      <c r="Z40" s="14" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA40" s="14" t="n">
         <v>9</v>
       </c>
@@ -9729,9 +9771,15 @@
       <c r="AE40" s="14" t="n">
         <v>52.72</v>
       </c>
-      <c r="AF40" s="14" t="n"/>
-      <c r="AG40" s="14" t="n"/>
-      <c r="AH40" s="14" t="n"/>
+      <c r="AF40" s="14" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="AG40" s="14" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AH40" s="14" t="n">
+        <v>71.47</v>
+      </c>
       <c r="AI40" s="14" t="n">
         <v>38.9</v>
       </c>
@@ -9761,7 +9809,7 @@
         <v>1</v>
       </c>
       <c r="AS40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT40" s="4" t="n">
         <v>0</v>
@@ -10007,9 +10055,11 @@
       </c>
       <c r="X42" s="12" t="n"/>
       <c r="Y42" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z42" s="14" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="Z42" s="14" t="n">
+        <v>28</v>
+      </c>
       <c r="AA42" s="14" t="n"/>
       <c r="AB42" s="14" t="n">
         <v>38</v>
@@ -10041,7 +10091,7 @@
         <v>1</v>
       </c>
       <c r="AS42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT42" s="4" t="n">
         <v>0</v>
@@ -10267,9 +10317,11 @@
         <v>0.00343</v>
       </c>
       <c r="Y44" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z44" s="14" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="Z44" s="14" t="n">
+        <v>10</v>
+      </c>
       <c r="AA44" s="14" t="n">
         <v>12.5</v>
       </c>
@@ -10285,9 +10337,15 @@
       <c r="AE44" s="14" t="n">
         <v>30.25</v>
       </c>
-      <c r="AF44" s="14" t="n"/>
-      <c r="AG44" s="14" t="n"/>
-      <c r="AH44" s="14" t="n"/>
+      <c r="AF44" s="14" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="AG44" s="14" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AH44" s="14" t="n">
+        <v>42.25</v>
+      </c>
       <c r="AI44" s="14" t="n"/>
       <c r="AJ44" s="14" t="n">
         <v>18</v>
@@ -10313,7 +10371,7 @@
         <v>1</v>
       </c>
       <c r="AS44" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT44" s="4" t="n">
         <v>0</v>
@@ -11785,9 +11843,11 @@
       </c>
       <c r="X55" s="12" t="n"/>
       <c r="Y55" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z55" s="14" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="Z55" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="AA55" s="14" t="n">
         <v>7.5</v>
       </c>
@@ -11803,9 +11863,15 @@
       <c r="AE55" s="14" t="n">
         <v>81.5</v>
       </c>
-      <c r="AF55" s="14" t="n"/>
-      <c r="AG55" s="14" t="n"/>
-      <c r="AH55" s="14" t="n"/>
+      <c r="AF55" s="14" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="AG55" s="14" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="AH55" s="14" t="n">
+        <v>86.5</v>
+      </c>
       <c r="AI55" s="14" t="n"/>
       <c r="AJ55" s="14" t="n"/>
       <c r="AK55" s="14" t="n"/>
@@ -11825,7 +11891,7 @@
         <v>1</v>
       </c>
       <c r="AS55" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT55" s="4" t="n">
         <v>1</v>

--- a/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_geral.xlsx
+++ b/dados/[B1] Estabelecimentos e cardapios/estabelecimentos/4_estatistica_descritiva/B1_estatistica_descritiva_geral.xlsx
@@ -6533,7 +6533,7 @@
       <c r="W18" s="9" t="n"/>
       <c r="X18" s="12" t="n"/>
       <c r="Y18" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z18" s="14" t="n">
         <v>22.5</v>
@@ -6554,13 +6554,13 @@
         <v>75.8</v>
       </c>
       <c r="AF18" s="14" t="n">
-        <v>88.05</v>
+        <v>86.8</v>
       </c>
       <c r="AG18" s="14" t="n">
         <v>95.8</v>
       </c>
       <c r="AH18" s="14" t="n">
-        <v>102.05</v>
+        <v>103.3</v>
       </c>
       <c r="AI18" s="14" t="n"/>
       <c r="AJ18" s="14" t="n"/>
@@ -10613,9 +10613,11 @@
         <v>0.00693</v>
       </c>
       <c r="Y46" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z46" s="14" t="n"/>
+        <v>93</v>
+      </c>
+      <c r="Z46" s="14" t="n">
+        <v>12.5</v>
+      </c>
       <c r="AA46" s="14" t="n">
         <v>16</v>
       </c>
@@ -10631,9 +10633,15 @@
       <c r="AE46" s="14" t="n">
         <v>57</v>
       </c>
-      <c r="AF46" s="14" t="n"/>
-      <c r="AG46" s="14" t="n"/>
-      <c r="AH46" s="14" t="n"/>
+      <c r="AF46" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="AG46" s="14" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AH46" s="14" t="n">
+        <v>70.75</v>
+      </c>
       <c r="AI46" s="14" t="n">
         <v>28</v>
       </c>
@@ -10663,7 +10671,7 @@
         <v>1</v>
       </c>
       <c r="AS46" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT46" s="4" t="n">
         <v>0</v>
